--- a/research/traditional_assets/database/data/iceland/iceland_healthcare_products.xlsx
+++ b/research/traditional_assets/database/data/iceland/iceland_healthcare_products.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1006327077842059</v>
+        <v>0.1004674423686375</v>
       </c>
       <c r="C2">
-        <v>2603.570105123651</v>
+        <v>2584.687494671411</v>
       </c>
       <c r="D2">
-        <v>2522.370105123651</v>
+        <v>2529.995494671411</v>
       </c>
       <c r="E2">
-        <v>-540.9</v>
+        <v>-514.3919999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>26.508</v>
       </c>
       <c r="G2">
         <v>81.2</v>
@@ -1451,28 +1451,28 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.3333524</v>
       </c>
       <c r="N2">
-        <v>108.6408163265306</v>
+        <v>107.3074639265306</v>
       </c>
       <c r="O2">
-        <v>21.72816326530612</v>
+        <v>21.46149278530612</v>
       </c>
       <c r="P2">
-        <v>86.91265306122449</v>
+        <v>85.8459711412245</v>
       </c>
       <c r="Q2">
-        <v>105.3126530612245</v>
+        <v>104.2459711412245</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1006327077842059</v>
+        <v>0.1010758003723611</v>
       </c>
       <c r="T2">
-        <v>1.040156204727314</v>
+        <v>1.048561507391778</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>81.47944708880459</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1004674423686375</v>
+        <v>0.1003021769530691</v>
       </c>
       <c r="C3">
-        <v>2584.687494671411</v>
+        <v>2565.851128726929</v>
       </c>
       <c r="D3">
-        <v>2529.995494671411</v>
+        <v>2537.66712872693</v>
       </c>
       <c r="E3">
-        <v>-514.3919999999999</v>
+        <v>-487.884</v>
       </c>
       <c r="F3">
-        <v>26.508</v>
+        <v>53.01600000000001</v>
       </c>
       <c r="G3">
         <v>81.2</v>
@@ -1533,28 +1533,28 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M3">
-        <v>1.3333524</v>
+        <v>2.6667048</v>
       </c>
       <c r="N3">
-        <v>107.3074639265306</v>
+        <v>105.9741115265306</v>
       </c>
       <c r="O3">
-        <v>21.46149278530612</v>
+        <v>21.19482230530612</v>
       </c>
       <c r="P3">
-        <v>85.8459711412245</v>
+        <v>84.77928922122449</v>
       </c>
       <c r="Q3">
-        <v>104.2459711412245</v>
+        <v>103.1792892212245</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1010758003723611</v>
+        <v>0.101527935666397</v>
       </c>
       <c r="T3">
-        <v>1.048561507391778</v>
+        <v>1.057138346845311</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>81.47944708880459</v>
+        <v>40.73972354440229</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1003021769530691</v>
+        <v>0.1001369115375007</v>
       </c>
       <c r="C4">
-        <v>2565.851128726929</v>
+        <v>2547.06142924745</v>
       </c>
       <c r="D4">
-        <v>2537.66712872693</v>
+        <v>2545.38542924745</v>
       </c>
       <c r="E4">
-        <v>-487.884</v>
+        <v>-461.376</v>
       </c>
       <c r="F4">
-        <v>53.01600000000001</v>
+        <v>79.524</v>
       </c>
       <c r="G4">
         <v>81.2</v>
@@ -1615,28 +1615,28 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M4">
-        <v>2.6667048</v>
+        <v>4.0000572</v>
       </c>
       <c r="N4">
-        <v>105.9741115265306</v>
+        <v>104.6407591265306</v>
       </c>
       <c r="O4">
-        <v>21.19482230530612</v>
+        <v>20.92815182530612</v>
       </c>
       <c r="P4">
-        <v>84.77928922122449</v>
+        <v>83.71260730122449</v>
       </c>
       <c r="Q4">
-        <v>103.1792892212245</v>
+        <v>102.1126073012245</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.101527935666397</v>
+        <v>0.1019893933376296</v>
       </c>
       <c r="T4">
-        <v>1.057138346845311</v>
+        <v>1.065892028349433</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>40.73972354440229</v>
+        <v>27.1598156962682</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1001369115375007</v>
+        <v>0.09997164612193227</v>
       </c>
       <c r="C5">
-        <v>2547.06142924745</v>
+        <v>2528.318823339398</v>
       </c>
       <c r="D5">
-        <v>2545.38542924745</v>
+        <v>2553.150823339398</v>
       </c>
       <c r="E5">
-        <v>-461.376</v>
+        <v>-434.8679999999999</v>
       </c>
       <c r="F5">
-        <v>79.524</v>
+        <v>106.032</v>
       </c>
       <c r="G5">
         <v>81.2</v>
@@ -1697,28 +1697,28 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M5">
-        <v>4.0000572</v>
+        <v>5.3334096</v>
       </c>
       <c r="N5">
-        <v>104.6407591265306</v>
+        <v>103.3074067265306</v>
       </c>
       <c r="O5">
-        <v>20.92815182530612</v>
+        <v>20.66148134530613</v>
       </c>
       <c r="P5">
-        <v>83.71260730122449</v>
+        <v>82.64592538122449</v>
       </c>
       <c r="Q5">
-        <v>102.1126073012245</v>
+        <v>101.0459253812245</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1019893933376296</v>
+        <v>0.1024604647103461</v>
       </c>
       <c r="T5">
-        <v>1.065892028349433</v>
+        <v>1.074828078218225</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>27.1598156962682</v>
+        <v>20.36986177220115</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09997164612193227</v>
+        <v>0.09980638070636384</v>
       </c>
       <c r="C6">
-        <v>2528.318823339398</v>
+        <v>2509.62374333717</v>
       </c>
       <c r="D6">
-        <v>2553.150823339398</v>
+        <v>2560.96374333717</v>
       </c>
       <c r="E6">
-        <v>-434.8679999999999</v>
+        <v>-408.36</v>
       </c>
       <c r="F6">
-        <v>106.032</v>
+        <v>132.54</v>
       </c>
       <c r="G6">
         <v>81.2</v>
@@ -1779,28 +1779,28 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M6">
-        <v>5.3334096</v>
+        <v>6.666762</v>
       </c>
       <c r="N6">
-        <v>103.3074067265306</v>
+        <v>101.9740543265306</v>
       </c>
       <c r="O6">
-        <v>20.66148134530613</v>
+        <v>20.39481086530612</v>
       </c>
       <c r="P6">
-        <v>82.64592538122449</v>
+        <v>81.57924346122448</v>
       </c>
       <c r="Q6">
-        <v>101.0459253812245</v>
+        <v>99.97924346122448</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1024604647103461</v>
+        <v>0.1029414533751198</v>
       </c>
       <c r="T6">
-        <v>1.074828078218225</v>
+        <v>1.083952255452675</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>20.36986177220115</v>
+        <v>16.29588941776092</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09980638070636384</v>
+        <v>0.09964111529079543</v>
       </c>
       <c r="C7">
-        <v>2509.62374333717</v>
+        <v>2490.976626883366</v>
       </c>
       <c r="D7">
-        <v>2560.96374333717</v>
+        <v>2568.824626883366</v>
       </c>
       <c r="E7">
-        <v>-408.36</v>
+        <v>-381.852</v>
       </c>
       <c r="F7">
-        <v>132.54</v>
+        <v>159.048</v>
       </c>
       <c r="G7">
         <v>81.2</v>
@@ -1861,28 +1861,28 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M7">
-        <v>6.666762</v>
+        <v>8.000114400000001</v>
       </c>
       <c r="N7">
-        <v>101.9740543265306</v>
+        <v>100.6407019265306</v>
       </c>
       <c r="O7">
-        <v>20.39481086530612</v>
+        <v>20.12814038530612</v>
       </c>
       <c r="P7">
-        <v>81.57924346122448</v>
+        <v>80.51256154122449</v>
       </c>
       <c r="Q7">
-        <v>99.97924346122448</v>
+        <v>98.91256154122449</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1029414533751198</v>
+        <v>0.1034326758412717</v>
       </c>
       <c r="T7">
-        <v>1.083952255452675</v>
+        <v>1.093270564117645</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>16.29588941776092</v>
+        <v>13.5799078481341</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09964111529079543</v>
+        <v>0.09955984987522702</v>
       </c>
       <c r="C8">
-        <v>2490.976626883366</v>
+        <v>2468.351759022138</v>
       </c>
       <c r="D8">
-        <v>2568.824626883366</v>
+        <v>2572.707759022138</v>
       </c>
       <c r="E8">
-        <v>-381.852</v>
+        <v>-355.344</v>
       </c>
       <c r="F8">
-        <v>159.048</v>
+        <v>185.556</v>
       </c>
       <c r="G8">
         <v>81.2</v>
@@ -1943,45 +1943,45 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M8">
-        <v>8.000114399999999</v>
+        <v>9.611800799999999</v>
       </c>
       <c r="N8">
-        <v>100.6407019265306</v>
+        <v>99.02901552653061</v>
       </c>
       <c r="O8">
-        <v>20.12814038530612</v>
+        <v>19.80580310530613</v>
       </c>
       <c r="P8">
-        <v>80.51256154122449</v>
+        <v>79.22321242122449</v>
       </c>
       <c r="Q8">
-        <v>98.91256154122449</v>
+        <v>97.62321242122449</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1034326758412717</v>
+        <v>0.1039344622314269</v>
       </c>
       <c r="T8">
-        <v>1.093270564117645</v>
+        <v>1.102789266517346</v>
       </c>
       <c r="U8">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V8">
         <v>0.2</v>
       </c>
       <c r="W8">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y8">
-        <v>13.5799078481341</v>
+        <v>11.30285766289816</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09955984987522702</v>
+        <v>0.09940658445965862</v>
       </c>
       <c r="C9">
-        <v>2468.351759022138</v>
+        <v>2449.19933162198</v>
       </c>
       <c r="D9">
-        <v>2572.707759022138</v>
+        <v>2580.06333162198</v>
       </c>
       <c r="E9">
-        <v>-355.3439999999999</v>
+        <v>-328.836</v>
       </c>
       <c r="F9">
-        <v>185.556</v>
+        <v>212.064</v>
       </c>
       <c r="G9">
         <v>81.2</v>
@@ -2025,28 +2025,28 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M9">
-        <v>9.611800800000001</v>
+        <v>10.9849152</v>
       </c>
       <c r="N9">
-        <v>99.02901552653061</v>
+        <v>97.65590112653061</v>
       </c>
       <c r="O9">
-        <v>19.80580310530613</v>
+        <v>19.53118022530612</v>
       </c>
       <c r="P9">
-        <v>79.22321242122449</v>
+        <v>78.12472090122449</v>
       </c>
       <c r="Q9">
-        <v>97.62321242122449</v>
+        <v>96.5247209012245</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1039344622314269</v>
+        <v>0.1044471570213681</v>
       </c>
       <c r="T9">
-        <v>1.102789266517346</v>
+        <v>1.112514897230084</v>
       </c>
       <c r="U9">
         <v>0.0518</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>11.30285766289815</v>
+        <v>9.890000455035883</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09940658445965862</v>
+        <v>0.0993757190440902</v>
       </c>
       <c r="C10">
-        <v>2449.19933162198</v>
+        <v>2424.177727480854</v>
       </c>
       <c r="D10">
-        <v>2580.06333162198</v>
+        <v>2581.549727480854</v>
       </c>
       <c r="E10">
-        <v>-328.836</v>
+        <v>-302.328</v>
       </c>
       <c r="F10">
-        <v>212.064</v>
+        <v>238.572</v>
       </c>
       <c r="G10">
         <v>81.2</v>
@@ -2107,45 +2107,45 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M10">
-        <v>10.9849152</v>
+        <v>12.763602</v>
       </c>
       <c r="N10">
-        <v>97.65590112653061</v>
+        <v>95.87721432653061</v>
       </c>
       <c r="O10">
-        <v>19.53118022530612</v>
+        <v>19.17544286530612</v>
       </c>
       <c r="P10">
-        <v>78.12472090122449</v>
+        <v>76.70177146122448</v>
       </c>
       <c r="Q10">
-        <v>96.5247209012245</v>
+        <v>95.10177146122449</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1044471570213681</v>
+        <v>0.1049711198286706</v>
       </c>
       <c r="T10">
-        <v>1.112514897230084</v>
+        <v>1.122454278068376</v>
       </c>
       <c r="U10">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V10">
         <v>0.2</v>
       </c>
       <c r="W10">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y10">
-        <v>9.890000455035883</v>
+        <v>8.511767785185608</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0993757190440902</v>
+        <v>0.09923605362852181</v>
       </c>
       <c r="C11">
-        <v>2424.177727480854</v>
+        <v>2404.417104785428</v>
       </c>
       <c r="D11">
-        <v>2581.549727480854</v>
+        <v>2588.297104785428</v>
       </c>
       <c r="E11">
-        <v>-302.328</v>
+        <v>-275.82</v>
       </c>
       <c r="F11">
-        <v>238.572</v>
+        <v>265.08</v>
       </c>
       <c r="G11">
         <v>81.2</v>
@@ -2189,28 +2189,28 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M11">
-        <v>12.763602</v>
+        <v>14.18178</v>
       </c>
       <c r="N11">
-        <v>95.87721432653061</v>
+        <v>94.45903632653061</v>
       </c>
       <c r="O11">
-        <v>19.17544286530612</v>
+        <v>18.89180726530612</v>
       </c>
       <c r="P11">
-        <v>76.70177146122448</v>
+        <v>75.56722906122448</v>
       </c>
       <c r="Q11">
-        <v>95.10177146122449</v>
+        <v>93.96722906122449</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1049711198286706</v>
+        <v>0.1055067262539131</v>
       </c>
       <c r="T11">
-        <v>1.122454278068376</v>
+        <v>1.132614534036409</v>
       </c>
       <c r="U11">
         <v>0.0535</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>8.511767785185608</v>
+        <v>7.660591006667049</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09923605362852181</v>
+        <v>0.09916678821295338</v>
       </c>
       <c r="C12">
-        <v>2404.417104785428</v>
+        <v>2381.268487663448</v>
       </c>
       <c r="D12">
-        <v>2588.297104785428</v>
+        <v>2591.656487663448</v>
       </c>
       <c r="E12">
-        <v>-275.8199999999999</v>
+        <v>-249.312</v>
       </c>
       <c r="F12">
-        <v>265.08</v>
+        <v>291.588</v>
       </c>
       <c r="G12">
         <v>81.2</v>
@@ -2271,45 +2271,45 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M12">
-        <v>14.18178</v>
+        <v>15.8332284</v>
       </c>
       <c r="N12">
-        <v>94.45903632653061</v>
+        <v>92.80758792653062</v>
       </c>
       <c r="O12">
-        <v>18.89180726530612</v>
+        <v>18.56151758530612</v>
       </c>
       <c r="P12">
-        <v>75.56722906122448</v>
+        <v>74.2460703412245</v>
       </c>
       <c r="Q12">
-        <v>93.96722906122449</v>
+        <v>92.6460703412245</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1055067262539131</v>
+        <v>0.1060543687785993</v>
       </c>
       <c r="T12">
-        <v>1.132614534036409</v>
+        <v>1.143003110363273</v>
       </c>
       <c r="U12">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V12">
         <v>0.2</v>
       </c>
       <c r="W12">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y12">
-        <v>7.660591006667048</v>
+        <v>6.861570715832698</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09916678821295338</v>
+        <v>0.09903352279738498</v>
       </c>
       <c r="C13">
-        <v>2381.268487663448</v>
+        <v>2361.248470436138</v>
       </c>
       <c r="D13">
-        <v>2591.656487663448</v>
+        <v>2598.144470436138</v>
       </c>
       <c r="E13">
-        <v>-249.312</v>
+        <v>-222.804</v>
       </c>
       <c r="F13">
-        <v>291.588</v>
+        <v>318.096</v>
       </c>
       <c r="G13">
         <v>81.2</v>
@@ -2353,28 +2353,28 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M13">
-        <v>15.8332284</v>
+        <v>17.2726128</v>
       </c>
       <c r="N13">
-        <v>92.80758792653062</v>
+        <v>91.36820352653061</v>
       </c>
       <c r="O13">
-        <v>18.56151758530612</v>
+        <v>18.27364070530612</v>
       </c>
       <c r="P13">
-        <v>74.2460703412245</v>
+        <v>73.09456282122449</v>
       </c>
       <c r="Q13">
-        <v>92.6460703412245</v>
+        <v>91.49456282122449</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1060543687785993</v>
+        <v>0.1066144577243011</v>
       </c>
       <c r="T13">
-        <v>1.143003110363273</v>
+        <v>1.153627790697567</v>
       </c>
       <c r="U13">
         <v>0.0543</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>6.861570715832698</v>
+        <v>6.289773156179973</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09903352279738498</v>
+        <v>0.09900425738181656</v>
       </c>
       <c r="C14">
-        <v>2361.248470436138</v>
+        <v>2336.169600009142</v>
       </c>
       <c r="D14">
-        <v>2598.144470436138</v>
+        <v>2599.573600009143</v>
       </c>
       <c r="E14">
-        <v>-222.804</v>
+        <v>-196.2959999999999</v>
       </c>
       <c r="F14">
-        <v>318.096</v>
+        <v>344.604</v>
       </c>
       <c r="G14">
         <v>81.2</v>
@@ -2435,45 +2435,45 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M14">
-        <v>17.2726128</v>
+        <v>19.0566012</v>
       </c>
       <c r="N14">
-        <v>91.36820352653061</v>
+        <v>89.58421512653061</v>
       </c>
       <c r="O14">
-        <v>18.27364070530612</v>
+        <v>17.91684302530612</v>
       </c>
       <c r="P14">
-        <v>73.09456282122449</v>
+        <v>71.66737210122449</v>
       </c>
       <c r="Q14">
-        <v>91.49456282122449</v>
+        <v>90.06737210122449</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1066144577243011</v>
+        <v>0.1071874222779501</v>
       </c>
       <c r="T14">
-        <v>1.153627790697567</v>
+        <v>1.164496716556786</v>
       </c>
       <c r="U14">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V14">
         <v>0.2</v>
       </c>
       <c r="W14">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y14">
-        <v>6.289773156179973</v>
+        <v>5.700954497936945</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09900425738181656</v>
+        <v>0.09887899196624816</v>
       </c>
       <c r="C15">
-        <v>2336.169600009142</v>
+        <v>2315.796544461608</v>
       </c>
       <c r="D15">
-        <v>2599.573600009143</v>
+        <v>2605.708544461608</v>
       </c>
       <c r="E15">
-        <v>-196.2959999999999</v>
+        <v>-169.7879999999999</v>
       </c>
       <c r="F15">
-        <v>344.604</v>
+        <v>371.1120000000001</v>
       </c>
       <c r="G15">
         <v>81.2</v>
@@ -2517,28 +2517,28 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M15">
-        <v>19.0566012</v>
+        <v>20.5224936</v>
       </c>
       <c r="N15">
-        <v>89.58421512653061</v>
+        <v>88.11832272653061</v>
       </c>
       <c r="O15">
-        <v>17.91684302530612</v>
+        <v>17.62366454530612</v>
       </c>
       <c r="P15">
-        <v>71.66737210122449</v>
+        <v>70.49465818122448</v>
       </c>
       <c r="Q15">
-        <v>90.06737210122449</v>
+        <v>88.89465818122449</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1071874222779501</v>
+        <v>0.1077737115886606</v>
       </c>
       <c r="T15">
-        <v>1.164496716556786</v>
+        <v>1.175618408133662</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.700954497936945</v>
+        <v>5.293743462370021</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09887899196624816</v>
+        <v>0.09875372655067974</v>
       </c>
       <c r="C16">
-        <v>2315.796544461608</v>
+        <v>2295.452514118394</v>
       </c>
       <c r="D16">
-        <v>2605.708544461608</v>
+        <v>2611.872514118395</v>
       </c>
       <c r="E16">
-        <v>-169.7879999999999</v>
+        <v>-143.2799999999999</v>
       </c>
       <c r="F16">
-        <v>371.1120000000001</v>
+        <v>397.6200000000001</v>
       </c>
       <c r="G16">
         <v>81.2</v>
@@ -2599,28 +2599,28 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M16">
-        <v>20.5224936</v>
+        <v>21.98838600000001</v>
       </c>
       <c r="N16">
-        <v>88.11832272653061</v>
+        <v>86.65243032653061</v>
       </c>
       <c r="O16">
-        <v>17.62366454530612</v>
+        <v>17.33048606530612</v>
       </c>
       <c r="P16">
-        <v>70.49465818122448</v>
+        <v>69.32194426122449</v>
       </c>
       <c r="Q16">
-        <v>88.89465818122449</v>
+        <v>87.72194426122449</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1077737115886606</v>
+        <v>0.1083737959419762</v>
       </c>
       <c r="T16">
-        <v>1.175618408133662</v>
+        <v>1.18700178657117</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.293743462370021</v>
+        <v>4.940827231545352</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09875372655067974</v>
+        <v>0.09862846113511131</v>
       </c>
       <c r="C17">
-        <v>2295.452514118394</v>
+        <v>2275.137715450835</v>
       </c>
       <c r="D17">
-        <v>2611.872514118395</v>
+        <v>2618.065715450836</v>
       </c>
       <c r="E17">
-        <v>-143.28</v>
+        <v>-116.7719999999999</v>
       </c>
       <c r="F17">
-        <v>397.62</v>
+        <v>424.128</v>
       </c>
       <c r="G17">
         <v>81.2</v>
@@ -2681,28 +2681,28 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M17">
-        <v>21.988386</v>
+        <v>23.4542784</v>
       </c>
       <c r="N17">
-        <v>86.65243032653061</v>
+        <v>85.1865379265306</v>
       </c>
       <c r="O17">
-        <v>17.33048606530612</v>
+        <v>17.03730758530612</v>
       </c>
       <c r="P17">
-        <v>69.32194426122449</v>
+        <v>68.14923034122448</v>
       </c>
       <c r="Q17">
-        <v>87.72194426122449</v>
+        <v>86.54923034122449</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1083737959419762</v>
+        <v>0.1089881680179897</v>
       </c>
       <c r="T17">
-        <v>1.18700178657117</v>
+        <v>1.198656197828619</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>4.940827231545353</v>
+        <v>4.632025529573768</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09862846113511131</v>
+        <v>0.09884319571954291</v>
       </c>
       <c r="C18">
-        <v>2275.137715450835</v>
+        <v>2238.031009136186</v>
       </c>
       <c r="D18">
-        <v>2618.065715450836</v>
+        <v>2607.467009136186</v>
       </c>
       <c r="E18">
-        <v>-116.7719999999999</v>
+        <v>-90.2639999999999</v>
       </c>
       <c r="F18">
-        <v>424.128</v>
+        <v>450.6360000000001</v>
       </c>
       <c r="G18">
         <v>81.2</v>
@@ -2763,45 +2763,45 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M18">
-        <v>23.4542784</v>
+        <v>26.0467608</v>
       </c>
       <c r="N18">
-        <v>85.1865379265306</v>
+        <v>82.59405552653061</v>
       </c>
       <c r="O18">
-        <v>17.03730758530612</v>
+        <v>16.51881110530612</v>
       </c>
       <c r="P18">
-        <v>68.14923034122448</v>
+        <v>66.07524442122448</v>
       </c>
       <c r="Q18">
-        <v>86.54923034122449</v>
+        <v>84.47524442122449</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1089881680179897</v>
+        <v>0.1096173442404131</v>
       </c>
       <c r="T18">
-        <v>1.198656197828619</v>
+        <v>1.210591438272995</v>
       </c>
       <c r="U18">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V18">
         <v>0.2</v>
       </c>
       <c r="W18">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y18">
-        <v>4.632025529573768</v>
+        <v>4.170991439616191</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09884319571954291</v>
+        <v>0.09924193030397449</v>
       </c>
       <c r="C19">
-        <v>2238.031009136186</v>
+        <v>2192.068485910821</v>
       </c>
       <c r="D19">
-        <v>2607.467009136186</v>
+        <v>2588.012485910822</v>
       </c>
       <c r="E19">
-        <v>-90.2639999999999</v>
+        <v>-63.75599999999991</v>
       </c>
       <c r="F19">
-        <v>450.6360000000001</v>
+        <v>477.1440000000001</v>
       </c>
       <c r="G19">
         <v>81.2</v>
@@ -2845,45 +2845,45 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M19">
-        <v>26.0467608</v>
+        <v>29.2489272</v>
       </c>
       <c r="N19">
-        <v>82.59405552653061</v>
+        <v>79.3918891265306</v>
       </c>
       <c r="O19">
-        <v>16.51881110530612</v>
+        <v>15.87837782530612</v>
       </c>
       <c r="P19">
-        <v>66.07524442122448</v>
+        <v>63.51351130122448</v>
       </c>
       <c r="Q19">
-        <v>84.47524442122449</v>
+        <v>81.91351130122449</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1096173442404131</v>
+        <v>0.1102618662243592</v>
       </c>
       <c r="T19">
-        <v>1.210591438272995</v>
+        <v>1.222817782142843</v>
       </c>
       <c r="U19">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>4.170991439616191</v>
+        <v>3.71435217379633</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09924193030397449</v>
+        <v>0.0991646648884061</v>
       </c>
       <c r="C20">
-        <v>2192.068485910821</v>
+        <v>2169.307606981257</v>
       </c>
       <c r="D20">
-        <v>2588.012485910822</v>
+        <v>2591.759606981258</v>
       </c>
       <c r="E20">
-        <v>-63.75599999999997</v>
+        <v>-37.24799999999993</v>
       </c>
       <c r="F20">
-        <v>477.144</v>
+        <v>503.652</v>
       </c>
       <c r="G20">
         <v>81.2</v>
@@ -2927,28 +2927,28 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M20">
-        <v>29.2489272</v>
+        <v>30.8738676</v>
       </c>
       <c r="N20">
-        <v>79.39188912653061</v>
+        <v>77.76694872653061</v>
       </c>
       <c r="O20">
-        <v>15.87837782530612</v>
+        <v>15.55338974530612</v>
       </c>
       <c r="P20">
-        <v>63.51351130122449</v>
+        <v>62.21355898122449</v>
       </c>
       <c r="Q20">
-        <v>81.9135113012245</v>
+        <v>80.6135589812245</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1102618662243591</v>
+        <v>0.1109223023313655</v>
       </c>
       <c r="T20">
-        <v>1.222817782142843</v>
+        <v>1.235346011046514</v>
       </c>
       <c r="U20">
         <v>0.0613</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.71435217379633</v>
+        <v>3.518859954122839</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0991646648884061</v>
+        <v>0.09953539947283768</v>
       </c>
       <c r="C21">
-        <v>2169.307606981257</v>
+        <v>2124.918379145099</v>
       </c>
       <c r="D21">
-        <v>2591.759606981258</v>
+        <v>2573.878379145099</v>
       </c>
       <c r="E21">
-        <v>-37.24799999999993</v>
+        <v>-10.7399999999999</v>
       </c>
       <c r="F21">
-        <v>503.652</v>
+        <v>530.1600000000001</v>
       </c>
       <c r="G21">
         <v>81.2</v>
@@ -3009,45 +3009,45 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M21">
-        <v>30.8738676</v>
+        <v>33.983256</v>
       </c>
       <c r="N21">
-        <v>77.76694872653061</v>
+        <v>74.65756032653061</v>
       </c>
       <c r="O21">
-        <v>15.55338974530612</v>
+        <v>14.93151206530612</v>
       </c>
       <c r="P21">
-        <v>62.21355898122449</v>
+        <v>59.72604826122449</v>
       </c>
       <c r="Q21">
-        <v>80.6135589812245</v>
+        <v>78.1260482612245</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1109223023313655</v>
+        <v>0.1115992493410471</v>
       </c>
       <c r="T21">
-        <v>1.235346011046514</v>
+        <v>1.248187445672777</v>
       </c>
       <c r="U21">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V21">
         <v>0.2</v>
       </c>
       <c r="W21">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y21">
-        <v>3.518859954122839</v>
+        <v>3.19689250278227</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09953539947283768</v>
+        <v>0.09948053405726928</v>
       </c>
       <c r="C22">
-        <v>2124.918379145099</v>
+        <v>2101.041070314148</v>
       </c>
       <c r="D22">
-        <v>2573.878379145099</v>
+        <v>2576.509070314149</v>
       </c>
       <c r="E22">
-        <v>-10.7399999999999</v>
+        <v>15.76800000000014</v>
       </c>
       <c r="F22">
-        <v>530.1600000000001</v>
+        <v>556.6680000000001</v>
       </c>
       <c r="G22">
         <v>81.2</v>
@@ -3091,28 +3091,28 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M22">
-        <v>33.983256</v>
+        <v>35.68241880000001</v>
       </c>
       <c r="N22">
-        <v>74.65756032653061</v>
+        <v>72.9583975265306</v>
       </c>
       <c r="O22">
-        <v>14.93151206530612</v>
+        <v>14.59167950530612</v>
       </c>
       <c r="P22">
-        <v>59.72604826122449</v>
+        <v>58.36671802122449</v>
       </c>
       <c r="Q22">
-        <v>78.1260482612245</v>
+        <v>76.76671802122449</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1115992493410471</v>
+        <v>0.1122933342497079</v>
       </c>
       <c r="T22">
-        <v>1.248187445672777</v>
+        <v>1.261353979909832</v>
       </c>
       <c r="U22">
         <v>0.0641</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.19689250278227</v>
+        <v>3.044659526459304</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09948053405726927</v>
+        <v>0.1007984686417009</v>
       </c>
       <c r="C23">
-        <v>2101.041070314149</v>
+        <v>2012.791889246173</v>
       </c>
       <c r="D23">
-        <v>2576.50907031415</v>
+        <v>2514.767889246173</v>
       </c>
       <c r="E23">
-        <v>15.76800000000003</v>
+        <v>42.27600000000007</v>
       </c>
       <c r="F23">
-        <v>556.668</v>
+        <v>583.176</v>
       </c>
       <c r="G23">
         <v>81.2</v>
@@ -3173,45 +3173,45 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M23">
-        <v>35.6824188</v>
+        <v>41.93035440000001</v>
       </c>
       <c r="N23">
-        <v>72.9583975265306</v>
+        <v>66.7104619265306</v>
       </c>
       <c r="O23">
-        <v>14.59167950530612</v>
+        <v>13.34209238530612</v>
       </c>
       <c r="P23">
-        <v>58.36671802122449</v>
+        <v>53.36836954122448</v>
       </c>
       <c r="Q23">
-        <v>76.76671802122449</v>
+        <v>71.76836954122449</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1122933342497079</v>
+        <v>0.1130052162073088</v>
       </c>
       <c r="T23">
-        <v>1.261353979909832</v>
+        <v>1.274858117588862</v>
       </c>
       <c r="U23">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V23">
         <v>0.2</v>
       </c>
       <c r="W23">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>3.044659526459305</v>
+        <v>2.590982544295657</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1007984686417009</v>
+        <v>0.1015236032261325</v>
       </c>
       <c r="C24">
-        <v>2012.791889246173</v>
+        <v>1953.559064167825</v>
       </c>
       <c r="D24">
-        <v>2514.767889246173</v>
+        <v>2482.043064167825</v>
       </c>
       <c r="E24">
-        <v>42.27600000000007</v>
+        <v>68.78400000000011</v>
       </c>
       <c r="F24">
-        <v>583.176</v>
+        <v>609.6840000000001</v>
       </c>
       <c r="G24">
         <v>81.2</v>
@@ -3255,45 +3255,45 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M24">
-        <v>41.93035440000001</v>
+        <v>46.21404720000001</v>
       </c>
       <c r="N24">
-        <v>66.7104619265306</v>
+        <v>62.4267691265306</v>
       </c>
       <c r="O24">
-        <v>13.34209238530612</v>
+        <v>12.48535382530612</v>
       </c>
       <c r="P24">
-        <v>53.36836954122448</v>
+        <v>49.94141530122448</v>
       </c>
       <c r="Q24">
-        <v>71.76836954122449</v>
+        <v>68.34141530122449</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1130052162073088</v>
+        <v>0.1137355886053668</v>
       </c>
       <c r="T24">
-        <v>1.274858117588862</v>
+        <v>1.288713012090725</v>
       </c>
       <c r="U24">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V24">
         <v>0.2</v>
       </c>
       <c r="W24">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y24">
-        <v>2.590982544295657</v>
+        <v>2.350818050112923</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1015236032261325</v>
+        <v>0.101562337810564</v>
       </c>
       <c r="C25">
-        <v>1953.559064167825</v>
+        <v>1925.326945158352</v>
       </c>
       <c r="D25">
-        <v>2482.043064167825</v>
+        <v>2480.318945158352</v>
       </c>
       <c r="E25">
-        <v>68.78400000000011</v>
+        <v>95.29200000000014</v>
       </c>
       <c r="F25">
-        <v>609.6840000000001</v>
+        <v>636.1920000000001</v>
       </c>
       <c r="G25">
         <v>81.2</v>
@@ -3337,28 +3337,28 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M25">
-        <v>46.21404720000001</v>
+        <v>48.22335360000001</v>
       </c>
       <c r="N25">
-        <v>62.4267691265306</v>
+        <v>60.4174627265306</v>
       </c>
       <c r="O25">
-        <v>12.48535382530612</v>
+        <v>12.08349254530612</v>
       </c>
       <c r="P25">
-        <v>49.94141530122448</v>
+        <v>48.33397018122448</v>
       </c>
       <c r="Q25">
-        <v>68.34141530122449</v>
+        <v>66.73397018122449</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1137355886053668</v>
+        <v>0.1144851813296895</v>
       </c>
       <c r="T25">
-        <v>1.288713012090725</v>
+        <v>1.302932509079478</v>
       </c>
       <c r="U25">
         <v>0.07580000000000001</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.350818050112923</v>
+        <v>2.252867298024885</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.101562337810564</v>
+        <v>0.1016010723949956</v>
       </c>
       <c r="C26">
-        <v>1925.326945158352</v>
+        <v>1897.097219759987</v>
       </c>
       <c r="D26">
-        <v>2480.318945158352</v>
+        <v>2478.597219759987</v>
       </c>
       <c r="E26">
-        <v>95.29200000000003</v>
+        <v>121.8000000000001</v>
       </c>
       <c r="F26">
-        <v>636.192</v>
+        <v>662.7</v>
       </c>
       <c r="G26">
         <v>81.2</v>
@@ -3419,28 +3419,28 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M26">
-        <v>48.2233536</v>
+        <v>50.23266000000001</v>
       </c>
       <c r="N26">
-        <v>60.41746272653061</v>
+        <v>58.4081563265306</v>
       </c>
       <c r="O26">
-        <v>12.08349254530612</v>
+        <v>11.68163126530612</v>
       </c>
       <c r="P26">
-        <v>48.33397018122449</v>
+        <v>46.72652506122448</v>
       </c>
       <c r="Q26">
-        <v>66.73397018122449</v>
+        <v>65.12652506122448</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1144851813296895</v>
+        <v>0.1152547631933275</v>
       </c>
       <c r="T26">
-        <v>1.302932509079478</v>
+        <v>1.317531192654598</v>
       </c>
       <c r="U26">
         <v>0.07580000000000001</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.252867298024885</v>
+        <v>2.162752606103889</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1016010723949956</v>
+        <v>0.1016398069794272</v>
       </c>
       <c r="C27">
-        <v>1897.097219759987</v>
+        <v>1868.869882991576</v>
       </c>
       <c r="D27">
-        <v>2478.597219759987</v>
+        <v>2476.877882991576</v>
       </c>
       <c r="E27">
-        <v>121.8000000000001</v>
+        <v>148.3080000000001</v>
       </c>
       <c r="F27">
-        <v>662.7</v>
+        <v>689.2080000000001</v>
       </c>
       <c r="G27">
         <v>81.2</v>
@@ -3501,28 +3501,28 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M27">
-        <v>50.23266000000001</v>
+        <v>52.24196640000001</v>
       </c>
       <c r="N27">
-        <v>58.4081563265306</v>
+        <v>56.3988499265306</v>
       </c>
       <c r="O27">
-        <v>11.68163126530612</v>
+        <v>11.27976998530612</v>
       </c>
       <c r="P27">
-        <v>46.72652506122448</v>
+        <v>45.11907994122448</v>
       </c>
       <c r="Q27">
-        <v>65.12652506122448</v>
+        <v>63.51907994122449</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1152547631933275</v>
+        <v>0.1160451445667935</v>
       </c>
       <c r="T27">
-        <v>1.317531192654598</v>
+        <v>1.332524435245262</v>
       </c>
       <c r="U27">
         <v>0.07580000000000001</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.162752606103889</v>
+        <v>2.079569813561432</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1016398069794272</v>
+        <v>0.1016785415638588</v>
       </c>
       <c r="C28">
-        <v>1868.869882991576</v>
+        <v>1840.644929885778</v>
       </c>
       <c r="D28">
-        <v>2476.877882991576</v>
+        <v>2475.160929885778</v>
       </c>
       <c r="E28">
-        <v>148.3080000000001</v>
+        <v>174.8160000000001</v>
       </c>
       <c r="F28">
-        <v>689.2080000000001</v>
+        <v>715.7160000000001</v>
       </c>
       <c r="G28">
         <v>81.2</v>
@@ -3583,28 +3583,28 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M28">
-        <v>52.24196640000001</v>
+        <v>54.25127280000002</v>
       </c>
       <c r="N28">
-        <v>56.3988499265306</v>
+        <v>54.38954352653059</v>
       </c>
       <c r="O28">
-        <v>11.27976998530612</v>
+        <v>10.87790870530612</v>
       </c>
       <c r="P28">
-        <v>45.11907994122448</v>
+        <v>43.51163482122448</v>
       </c>
       <c r="Q28">
-        <v>63.51907994122449</v>
+        <v>61.91163482122448</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1160451445667935</v>
+        <v>0.1168571802244641</v>
       </c>
       <c r="T28">
-        <v>1.332524435245262</v>
+        <v>1.347928451605533</v>
       </c>
       <c r="U28">
         <v>0.07580000000000001</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.079569813561432</v>
+        <v>2.002548709355453</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1016785415638588</v>
+        <v>0.1048980761482904</v>
       </c>
       <c r="C29">
-        <v>1840.644929885778</v>
+        <v>1679.295548656964</v>
       </c>
       <c r="D29">
-        <v>2475.160929885778</v>
+        <v>2340.319548656965</v>
       </c>
       <c r="E29">
-        <v>174.8160000000001</v>
+        <v>201.3240000000002</v>
       </c>
       <c r="F29">
-        <v>715.7160000000001</v>
+        <v>742.2240000000002</v>
       </c>
       <c r="G29">
         <v>81.2</v>
@@ -3665,45 +3665,45 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M29">
-        <v>54.25127280000002</v>
+        <v>66.80016000000001</v>
       </c>
       <c r="N29">
-        <v>54.38954352653059</v>
+        <v>41.84065632653061</v>
       </c>
       <c r="O29">
-        <v>10.87790870530612</v>
+        <v>8.368131265306122</v>
       </c>
       <c r="P29">
-        <v>43.51163482122448</v>
+        <v>33.47252506122449</v>
       </c>
       <c r="Q29">
-        <v>61.91163482122448</v>
+        <v>51.87252506122449</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1168571802244641</v>
+        <v>0.1176917724281811</v>
       </c>
       <c r="T29">
-        <v>1.347928451605533</v>
+        <v>1.363760357309145</v>
       </c>
       <c r="U29">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V29">
         <v>0.2</v>
       </c>
       <c r="W29">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y29">
-        <v>2.002548709355453</v>
+        <v>1.626355630383679</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1048980761482904</v>
+        <v>0.105050410732722</v>
       </c>
       <c r="C30">
-        <v>1679.295548656964</v>
+        <v>1646.770516851227</v>
       </c>
       <c r="D30">
-        <v>2340.319548656965</v>
+        <v>2334.302516851228</v>
       </c>
       <c r="E30">
-        <v>201.3240000000002</v>
+        <v>227.8320000000002</v>
       </c>
       <c r="F30">
-        <v>742.2240000000002</v>
+        <v>768.7320000000002</v>
       </c>
       <c r="G30">
         <v>81.2</v>
@@ -3747,28 +3747,28 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M30">
-        <v>66.80016000000001</v>
+        <v>69.18588000000001</v>
       </c>
       <c r="N30">
-        <v>41.84065632653061</v>
+        <v>39.4549363265306</v>
       </c>
       <c r="O30">
-        <v>8.368131265306122</v>
+        <v>7.89098726530612</v>
       </c>
       <c r="P30">
-        <v>33.47252506122449</v>
+        <v>31.56394906122448</v>
       </c>
       <c r="Q30">
-        <v>51.87252506122449</v>
+        <v>49.96394906122448</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1176917724281811</v>
+        <v>0.1185498742714394</v>
       </c>
       <c r="T30">
-        <v>1.363760357309145</v>
+        <v>1.380038232187507</v>
       </c>
       <c r="U30">
         <v>0.09</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>1.626355630383679</v>
+        <v>1.570274401749759</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.105050410732722</v>
+        <v>0.1052027453171536</v>
       </c>
       <c r="C31">
-        <v>1646.770516851228</v>
+        <v>1614.276345640729</v>
       </c>
       <c r="D31">
-        <v>2334.302516851228</v>
+        <v>2328.316345640729</v>
       </c>
       <c r="E31">
-        <v>227.832</v>
+        <v>254.34</v>
       </c>
       <c r="F31">
-        <v>768.732</v>
+        <v>795.24</v>
       </c>
       <c r="G31">
         <v>81.2</v>
@@ -3829,28 +3829,28 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M31">
-        <v>69.18588</v>
+        <v>71.5716</v>
       </c>
       <c r="N31">
-        <v>39.45493632653061</v>
+        <v>37.06921632653061</v>
       </c>
       <c r="O31">
-        <v>7.890987265306123</v>
+        <v>7.413843265306122</v>
       </c>
       <c r="P31">
-        <v>31.56394906122449</v>
+        <v>29.65537306122449</v>
       </c>
       <c r="Q31">
-        <v>49.9639490612245</v>
+        <v>48.05537306122449</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1185498742714394</v>
+        <v>0.1194324933102194</v>
       </c>
       <c r="T31">
-        <v>1.380038232187507</v>
+        <v>1.396781189205251</v>
       </c>
       <c r="U31">
         <v>0.09</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>1.570274401749759</v>
+        <v>1.517931921691434</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1052027453171536</v>
+        <v>0.1206841961530429</v>
       </c>
       <c r="C32">
-        <v>1614.276345640729</v>
+        <v>1106.415578472514</v>
       </c>
       <c r="D32">
-        <v>2328.316345640729</v>
+        <v>1846.963578472514</v>
       </c>
       <c r="E32">
-        <v>254.34</v>
+        <v>280.8480000000001</v>
       </c>
       <c r="F32">
-        <v>795.24</v>
+        <v>821.748</v>
       </c>
       <c r="G32">
         <v>81.2</v>
@@ -3911,45 +3911,45 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M32">
-        <v>71.5716</v>
+        <v>120.6326064</v>
       </c>
       <c r="N32">
-        <v>37.06921632653061</v>
+        <v>-11.9917900734694</v>
       </c>
       <c r="O32">
-        <v>7.413843265306122</v>
+        <v>-2.398358014693881</v>
       </c>
       <c r="P32">
-        <v>29.65537306122449</v>
+        <v>-9.593432058775523</v>
       </c>
       <c r="Q32">
-        <v>48.05537306122449</v>
+        <v>8.806567941224483</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1194324933102194</v>
+        <v>0.1208304761306908</v>
       </c>
       <c r="T32">
-        <v>1.396781189205251</v>
+        <v>1.423300406722982</v>
       </c>
       <c r="U32">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V32">
-        <v>0.2</v>
+        <v>0.180118492949234</v>
       </c>
       <c r="W32">
-        <v>0.07199999999999999</v>
+        <v>0.1203586052350525</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y32">
-        <v>1.517931921691434</v>
+        <v>0.9005924647461699</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1206841961530429</v>
+        <v>0.1216941961530429</v>
       </c>
       <c r="C33">
-        <v>1106.415578472514</v>
+        <v>1055.328186255282</v>
       </c>
       <c r="D33">
-        <v>1846.963578472514</v>
+        <v>1822.384186255282</v>
       </c>
       <c r="E33">
-        <v>280.8480000000001</v>
+        <v>307.3560000000001</v>
       </c>
       <c r="F33">
-        <v>821.748</v>
+        <v>848.2560000000001</v>
       </c>
       <c r="G33">
         <v>81.2</v>
@@ -3993,37 +3993,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M33">
-        <v>120.6326064</v>
+        <v>124.5239808</v>
       </c>
       <c r="N33">
-        <v>-11.9917900734694</v>
+        <v>-15.88316447346941</v>
       </c>
       <c r="O33">
-        <v>-2.398358014693881</v>
+        <v>-3.176632894693881</v>
       </c>
       <c r="P33">
-        <v>-9.593432058775523</v>
+        <v>-12.70653157877553</v>
       </c>
       <c r="Q33">
-        <v>8.806567941224483</v>
+        <v>5.69346842122448</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1208304761306908</v>
+        <v>0.1219338654855539</v>
       </c>
       <c r="T33">
-        <v>1.423300406722982</v>
+        <v>1.444231295057144</v>
       </c>
       <c r="U33">
         <v>0.1468</v>
       </c>
       <c r="V33">
-        <v>0.180118492949234</v>
+        <v>0.1744897900445704</v>
       </c>
       <c r="W33">
-        <v>0.1203586052350525</v>
+        <v>0.1211848988214571</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.9005924647461699</v>
+        <v>0.8724489502228522</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1216941961530429</v>
+        <v>0.1227041961530429</v>
       </c>
       <c r="C34">
-        <v>1055.328186255282</v>
+        <v>1004.886407343466</v>
       </c>
       <c r="D34">
-        <v>1822.384186255282</v>
+        <v>1798.450407343466</v>
       </c>
       <c r="E34">
-        <v>307.3560000000001</v>
+        <v>333.8640000000001</v>
       </c>
       <c r="F34">
-        <v>848.2560000000001</v>
+        <v>874.7640000000001</v>
       </c>
       <c r="G34">
         <v>81.2</v>
@@ -4075,37 +4075,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M34">
-        <v>124.5239808</v>
+        <v>128.4153552</v>
       </c>
       <c r="N34">
-        <v>-15.88316447346941</v>
+        <v>-19.77453887346941</v>
       </c>
       <c r="O34">
-        <v>-3.176632894693881</v>
+        <v>-3.954907774693882</v>
       </c>
       <c r="P34">
-        <v>-12.70653157877553</v>
+        <v>-15.81963109877553</v>
       </c>
       <c r="Q34">
-        <v>5.69346842122448</v>
+        <v>2.580368901224478</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1219338654855539</v>
+        <v>0.1230701918360846</v>
       </c>
       <c r="T34">
-        <v>1.444231295057144</v>
+        <v>1.465786986028146</v>
       </c>
       <c r="U34">
         <v>0.1468</v>
       </c>
       <c r="V34">
-        <v>0.1744897900445704</v>
+        <v>0.1692022206492804</v>
       </c>
       <c r="W34">
-        <v>0.1211848988214571</v>
+        <v>0.1219611140086856</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.8724489502228522</v>
+        <v>0.8460111032464021</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1227041961530429</v>
+        <v>0.1237141961530429</v>
       </c>
       <c r="C35">
-        <v>1004.886407343466</v>
+        <v>955.0651345241072</v>
       </c>
       <c r="D35">
-        <v>1798.450407343466</v>
+        <v>1775.137134524107</v>
       </c>
       <c r="E35">
-        <v>333.8640000000001</v>
+        <v>360.3720000000002</v>
       </c>
       <c r="F35">
-        <v>874.7640000000001</v>
+        <v>901.2720000000002</v>
       </c>
       <c r="G35">
         <v>81.2</v>
@@ -4157,37 +4157,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M35">
-        <v>128.4153552</v>
+        <v>132.3067296</v>
       </c>
       <c r="N35">
-        <v>-19.77453887346941</v>
+        <v>-23.66591327346943</v>
       </c>
       <c r="O35">
-        <v>-3.954907774693882</v>
+        <v>-4.733182654693886</v>
       </c>
       <c r="P35">
-        <v>-15.81963109877553</v>
+        <v>-18.93273061877554</v>
       </c>
       <c r="Q35">
-        <v>2.580368901224478</v>
+        <v>-0.5327306187755383</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1230701918360846</v>
+        <v>0.1242409523184495</v>
       </c>
       <c r="T35">
-        <v>1.465786986028146</v>
+        <v>1.487995879755845</v>
       </c>
       <c r="U35">
         <v>0.1468</v>
       </c>
       <c r="V35">
-        <v>0.1692022206492804</v>
+        <v>0.164225684747831</v>
       </c>
       <c r="W35">
-        <v>0.1219611140086856</v>
+        <v>0.1226916694790184</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.8460111032464021</v>
+        <v>0.8211284237391548</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1237141961530429</v>
+        <v>0.1444475561117958</v>
       </c>
       <c r="C36">
-        <v>955.0651345241072</v>
+        <v>555.4657105001065</v>
       </c>
       <c r="D36">
-        <v>1775.137134524107</v>
+        <v>1402.045710500107</v>
       </c>
       <c r="E36">
-        <v>360.3720000000002</v>
+        <v>386.8800000000002</v>
       </c>
       <c r="F36">
-        <v>901.2720000000002</v>
+        <v>927.7800000000002</v>
       </c>
       <c r="G36">
         <v>81.2</v>
@@ -4239,45 +4239,45 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M36">
-        <v>132.3067296</v>
+        <v>186.298224</v>
       </c>
       <c r="N36">
-        <v>-23.66591327346943</v>
+        <v>-77.65740767346942</v>
       </c>
       <c r="O36">
-        <v>-4.733182654693886</v>
+        <v>-15.53148153469389</v>
       </c>
       <c r="P36">
-        <v>-18.93273061877554</v>
+        <v>-62.12592613877554</v>
       </c>
       <c r="Q36">
-        <v>-0.5327306187755383</v>
+        <v>-43.72592613877553</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1242409523184495</v>
+        <v>0.1267144438291224</v>
       </c>
       <c r="T36">
-        <v>1.487995879755845</v>
+        <v>1.53491709970165</v>
       </c>
       <c r="U36">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V36">
-        <v>0.164225684747831</v>
+        <v>0.1166310810633714</v>
       </c>
       <c r="W36">
-        <v>0.1226916694790184</v>
+        <v>0.177380478922475</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y36">
-        <v>0.8211284237391548</v>
+        <v>0.5831554053168568</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1444475561117958</v>
+        <v>0.1459975561117958</v>
       </c>
       <c r="C37">
-        <v>555.4657105001065</v>
+        <v>507.268849657528</v>
       </c>
       <c r="D37">
-        <v>1402.045710500107</v>
+        <v>1380.356849657528</v>
       </c>
       <c r="E37">
-        <v>386.8800000000002</v>
+        <v>413.3880000000001</v>
       </c>
       <c r="F37">
-        <v>927.7800000000002</v>
+        <v>954.2880000000001</v>
       </c>
       <c r="G37">
         <v>81.2</v>
@@ -4321,37 +4321,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M37">
-        <v>186.298224</v>
+        <v>191.6210304</v>
       </c>
       <c r="N37">
-        <v>-77.65740767346942</v>
+        <v>-82.98021407346941</v>
       </c>
       <c r="O37">
-        <v>-15.53148153469389</v>
+        <v>-16.59604281469388</v>
       </c>
       <c r="P37">
-        <v>-62.12592613877554</v>
+        <v>-66.38417125877552</v>
       </c>
       <c r="Q37">
-        <v>-43.72592613877553</v>
+        <v>-47.98417125877552</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1267144438291224</v>
+        <v>0.1279787320139524</v>
       </c>
       <c r="T37">
-        <v>1.53491709970165</v>
+        <v>1.558900179384488</v>
       </c>
       <c r="U37">
         <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.1166310810633714</v>
+        <v>0.1133913288116111</v>
       </c>
       <c r="W37">
-        <v>0.177380478922475</v>
+        <v>0.1780310211746285</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.5831554053168568</v>
+        <v>0.5669566440580553</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1459975561117958</v>
+        <v>0.1475475561117958</v>
       </c>
       <c r="C38">
-        <v>507.2688496575281</v>
+        <v>459.7327955328833</v>
       </c>
       <c r="D38">
-        <v>1380.356849657528</v>
+        <v>1359.328795532883</v>
       </c>
       <c r="E38">
-        <v>413.388</v>
+        <v>439.8960000000001</v>
       </c>
       <c r="F38">
-        <v>954.288</v>
+        <v>980.796</v>
       </c>
       <c r="G38">
         <v>81.2</v>
@@ -4403,37 +4403,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M38">
-        <v>191.6210304</v>
+        <v>196.9438368</v>
       </c>
       <c r="N38">
-        <v>-82.98021407346938</v>
+        <v>-88.3030204734694</v>
       </c>
       <c r="O38">
-        <v>-16.59604281469388</v>
+        <v>-17.66060409469388</v>
       </c>
       <c r="P38">
-        <v>-66.38417125877551</v>
+        <v>-70.64241637877552</v>
       </c>
       <c r="Q38">
-        <v>-47.9841712587755</v>
+        <v>-52.24241637877552</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1279787320139524</v>
+        <v>0.1292831563316342</v>
       </c>
       <c r="T38">
-        <v>1.558900179384488</v>
+        <v>1.583644626676305</v>
       </c>
       <c r="U38">
         <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.1133913288116111</v>
+        <v>0.1103266983031892</v>
       </c>
       <c r="W38">
-        <v>0.1780310211746285</v>
+        <v>0.1786463989807196</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.5669566440580553</v>
+        <v>0.5516334915159458</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1475475561117958</v>
+        <v>0.1490975561117958</v>
       </c>
       <c r="C39">
-        <v>459.7327955328833</v>
+        <v>412.8278015246642</v>
       </c>
       <c r="D39">
-        <v>1359.328795532883</v>
+        <v>1338.931801524664</v>
       </c>
       <c r="E39">
-        <v>439.8960000000001</v>
+        <v>466.4040000000001</v>
       </c>
       <c r="F39">
-        <v>980.796</v>
+        <v>1007.304</v>
       </c>
       <c r="G39">
         <v>81.2</v>
@@ -4485,37 +4485,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M39">
-        <v>196.9438368</v>
+        <v>202.2666432</v>
       </c>
       <c r="N39">
-        <v>-88.3030204734694</v>
+        <v>-93.62582687346942</v>
       </c>
       <c r="O39">
-        <v>-17.66060409469388</v>
+        <v>-18.72516537469388</v>
       </c>
       <c r="P39">
-        <v>-70.64241637877552</v>
+        <v>-74.90066149877553</v>
       </c>
       <c r="Q39">
-        <v>-52.24241637877552</v>
+        <v>-56.50066149877553</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1292831563316342</v>
+        <v>0.1306296588531122</v>
       </c>
       <c r="T39">
-        <v>1.583644626676305</v>
+        <v>1.609187281945278</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.1103266983031892</v>
+        <v>0.1074233641373157</v>
       </c>
       <c r="W39">
-        <v>0.1786463989807196</v>
+        <v>0.179229388481227</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.5516334915159458</v>
+        <v>0.5371168206865786</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1490975561117958</v>
+        <v>0.1506475561117958</v>
       </c>
       <c r="C40">
-        <v>412.8278015246642</v>
+        <v>366.5258800511838</v>
       </c>
       <c r="D40">
-        <v>1338.931801524664</v>
+        <v>1319.137880051184</v>
       </c>
       <c r="E40">
-        <v>466.4040000000001</v>
+        <v>492.9120000000001</v>
       </c>
       <c r="F40">
-        <v>1007.304</v>
+        <v>1033.812</v>
       </c>
       <c r="G40">
         <v>81.2</v>
@@ -4567,37 +4567,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M40">
-        <v>202.2666432</v>
+        <v>207.5894496</v>
       </c>
       <c r="N40">
-        <v>-93.62582687346942</v>
+        <v>-98.94863327346941</v>
       </c>
       <c r="O40">
-        <v>-18.72516537469388</v>
+        <v>-19.78972665469388</v>
       </c>
       <c r="P40">
-        <v>-74.90066149877553</v>
+        <v>-79.15890661877553</v>
       </c>
       <c r="Q40">
-        <v>-56.50066149877553</v>
+        <v>-60.75890661877553</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1306296588531122</v>
+        <v>0.1320203089982452</v>
       </c>
       <c r="T40">
-        <v>1.609187281945278</v>
+        <v>1.63556740132143</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.1074233641373157</v>
+        <v>0.1046689189030256</v>
       </c>
       <c r="W40">
-        <v>0.179229388481227</v>
+        <v>0.1797824810842724</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.5371168206865786</v>
+        <v>0.523344594515128</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1506475561117958</v>
+        <v>0.1521975561117958</v>
       </c>
       <c r="C41">
-        <v>366.5258800511838</v>
+        <v>320.8006744235381</v>
       </c>
       <c r="D41">
-        <v>1319.137880051184</v>
+        <v>1299.920674423538</v>
       </c>
       <c r="E41">
-        <v>492.9120000000001</v>
+        <v>519.4200000000002</v>
       </c>
       <c r="F41">
-        <v>1033.812</v>
+        <v>1060.32</v>
       </c>
       <c r="G41">
         <v>81.2</v>
@@ -4649,37 +4649,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M41">
-        <v>207.5894496</v>
+        <v>212.912256</v>
       </c>
       <c r="N41">
-        <v>-98.94863327346941</v>
+        <v>-104.2714396734694</v>
       </c>
       <c r="O41">
-        <v>-19.78972665469388</v>
+        <v>-20.85428793469389</v>
       </c>
       <c r="P41">
-        <v>-79.15890661877553</v>
+        <v>-83.41715173877554</v>
       </c>
       <c r="Q41">
-        <v>-60.75890661877553</v>
+        <v>-65.01715173877554</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1320203089982452</v>
+        <v>0.1334573141482159</v>
       </c>
       <c r="T41">
-        <v>1.63556740132143</v>
+        <v>1.662826858010121</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.1046689189030256</v>
+        <v>0.10205219593045</v>
       </c>
       <c r="W41">
-        <v>0.1797824810842724</v>
+        <v>0.1803079190571657</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.523344594515128</v>
+        <v>0.5102609796522497</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1521975561117958</v>
+        <v>0.168429791800238</v>
       </c>
       <c r="C42">
-        <v>320.8006744235381</v>
+        <v>122.2250352817039</v>
       </c>
       <c r="D42">
-        <v>1299.920674423538</v>
+        <v>1127.853035281704</v>
       </c>
       <c r="E42">
-        <v>519.4200000000002</v>
+        <v>545.9280000000002</v>
       </c>
       <c r="F42">
-        <v>1060.32</v>
+        <v>1086.828</v>
       </c>
       <c r="G42">
         <v>81.2</v>
@@ -4731,45 +4731,45 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M42">
-        <v>212.912256</v>
+        <v>256.2740424</v>
       </c>
       <c r="N42">
-        <v>-104.2714396734694</v>
+        <v>-147.6332260734694</v>
       </c>
       <c r="O42">
-        <v>-20.85428793469389</v>
+        <v>-29.52664521469389</v>
       </c>
       <c r="P42">
-        <v>-83.41715173877554</v>
+        <v>-118.1065808587755</v>
       </c>
       <c r="Q42">
-        <v>-65.01715173877554</v>
+        <v>-99.70658085877552</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1334573141482159</v>
+        <v>0.1355061426735115</v>
       </c>
       <c r="T42">
-        <v>1.662826858010121</v>
+        <v>1.701692378045998</v>
       </c>
       <c r="U42">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.10205219593045</v>
+        <v>0.08478487739851612</v>
       </c>
       <c r="W42">
-        <v>0.1803079190571657</v>
+        <v>0.2158077259094299</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y42">
-        <v>0.5102609796522497</v>
+        <v>0.4239243869925806</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.168429791800238</v>
+        <v>0.1703297918002381</v>
       </c>
       <c r="C43">
-        <v>122.2250352817039</v>
+        <v>78.50893803801137</v>
       </c>
       <c r="D43">
-        <v>1127.853035281704</v>
+        <v>1110.644938038012</v>
       </c>
       <c r="E43">
-        <v>545.9280000000002</v>
+        <v>572.4360000000003</v>
       </c>
       <c r="F43">
-        <v>1086.828</v>
+        <v>1113.336</v>
       </c>
       <c r="G43">
         <v>81.2</v>
@@ -4813,37 +4813,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M43">
-        <v>256.2740424</v>
+        <v>262.5246288000001</v>
       </c>
       <c r="N43">
-        <v>-147.6332260734694</v>
+        <v>-153.8838124734694</v>
       </c>
       <c r="O43">
-        <v>-29.52664521469389</v>
+        <v>-30.77676249469389</v>
       </c>
       <c r="P43">
-        <v>-118.1065808587755</v>
+        <v>-123.1070499787756</v>
       </c>
       <c r="Q43">
-        <v>-99.70658085877552</v>
+        <v>-104.7070499787756</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1355061426735115</v>
+        <v>0.1370528003058134</v>
       </c>
       <c r="T43">
-        <v>1.701692378045998</v>
+        <v>1.731031901805412</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.08478487739851612</v>
+        <v>0.08276618984140859</v>
       </c>
       <c r="W43">
-        <v>0.2158077259094299</v>
+        <v>0.2162837324353959</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.4239243869925806</v>
+        <v>0.4138309492070429</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.170329791800238</v>
+        <v>0.172229791800238</v>
       </c>
       <c r="C44">
-        <v>78.50893803801182</v>
+        <v>35.31005092806186</v>
       </c>
       <c r="D44">
-        <v>1110.644938038012</v>
+        <v>1093.954050928062</v>
       </c>
       <c r="E44">
-        <v>572.436</v>
+        <v>598.9440000000001</v>
       </c>
       <c r="F44">
-        <v>1113.336</v>
+        <v>1139.844</v>
       </c>
       <c r="G44">
         <v>81.2</v>
@@ -4895,37 +4895,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M44">
-        <v>262.5246288</v>
+        <v>268.7752152</v>
       </c>
       <c r="N44">
-        <v>-153.8838124734694</v>
+        <v>-160.1343988734694</v>
       </c>
       <c r="O44">
-        <v>-30.77676249469388</v>
+        <v>-32.02687977469389</v>
       </c>
       <c r="P44">
-        <v>-123.1070499787755</v>
+        <v>-128.1075190987755</v>
       </c>
       <c r="Q44">
-        <v>-104.7070499787755</v>
+        <v>-109.7075190987755</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1370528003058134</v>
+        <v>0.138653726626968</v>
       </c>
       <c r="T44">
-        <v>1.731031901805411</v>
+        <v>1.76140088253884</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.0827661898414086</v>
+        <v>0.08084139472881768</v>
       </c>
       <c r="W44">
-        <v>0.2162837324353959</v>
+        <v>0.2167375991229448</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.413830949207043</v>
+        <v>0.4042069736440884</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.172229791800238</v>
+        <v>0.174129791800238</v>
       </c>
       <c r="C45">
-        <v>35.31005092806186</v>
+        <v>-7.394598872467441</v>
       </c>
       <c r="D45">
-        <v>1093.954050928062</v>
+        <v>1077.757401127533</v>
       </c>
       <c r="E45">
-        <v>598.9440000000001</v>
+        <v>625.4520000000001</v>
       </c>
       <c r="F45">
-        <v>1139.844</v>
+        <v>1166.352</v>
       </c>
       <c r="G45">
         <v>81.2</v>
@@ -4977,37 +4977,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M45">
-        <v>268.7752152</v>
+        <v>275.0258016</v>
       </c>
       <c r="N45">
-        <v>-160.1343988734694</v>
+        <v>-166.3849852734694</v>
       </c>
       <c r="O45">
-        <v>-32.02687977469389</v>
+        <v>-33.27699705469388</v>
       </c>
       <c r="P45">
-        <v>-128.1075190987755</v>
+        <v>-133.1079882187755</v>
       </c>
       <c r="Q45">
-        <v>-109.7075190987755</v>
+        <v>-114.7079882187755</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.138653726626968</v>
+        <v>0.1403118288881639</v>
       </c>
       <c r="T45">
-        <v>1.76140088253884</v>
+        <v>1.792854469727033</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.08084139472881768</v>
+        <v>0.07900409030316274</v>
       </c>
       <c r="W45">
-        <v>0.2167375991229448</v>
+        <v>0.2171708355065142</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.4042069736440884</v>
+        <v>0.3950204515158138</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.174129791800238</v>
+        <v>0.176029791800238</v>
       </c>
       <c r="C46">
-        <v>-7.394598872467441</v>
+        <v>-49.62664353103082</v>
       </c>
       <c r="D46">
-        <v>1077.757401127533</v>
+        <v>1062.033356468969</v>
       </c>
       <c r="E46">
-        <v>625.4520000000001</v>
+        <v>651.9600000000002</v>
       </c>
       <c r="F46">
-        <v>1166.352</v>
+        <v>1192.86</v>
       </c>
       <c r="G46">
         <v>81.2</v>
@@ -5059,37 +5059,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M46">
-        <v>275.0258016</v>
+        <v>281.2763880000001</v>
       </c>
       <c r="N46">
-        <v>-166.3849852734694</v>
+        <v>-172.6355716734694</v>
       </c>
       <c r="O46">
-        <v>-33.27699705469388</v>
+        <v>-34.52711433469388</v>
       </c>
       <c r="P46">
-        <v>-133.1079882187755</v>
+        <v>-138.1084573387755</v>
       </c>
       <c r="Q46">
-        <v>-114.7079882187755</v>
+        <v>-119.7084573387755</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1403118288881639</v>
+        <v>0.1420302257770396</v>
       </c>
       <c r="T46">
-        <v>1.792854469727033</v>
+        <v>1.82545182372207</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.07900409030316274</v>
+        <v>0.07724844385198135</v>
       </c>
       <c r="W46">
-        <v>0.2171708355065142</v>
+        <v>0.2175848169397028</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3950204515158138</v>
+        <v>0.3862422192599068</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.176029791800238</v>
+        <v>0.177929791800238</v>
       </c>
       <c r="C47">
-        <v>-49.62664353103082</v>
+        <v>-91.40647095010195</v>
       </c>
       <c r="D47">
-        <v>1062.033356468969</v>
+        <v>1046.761529049898</v>
       </c>
       <c r="E47">
-        <v>651.9600000000002</v>
+        <v>678.4680000000002</v>
       </c>
       <c r="F47">
-        <v>1192.86</v>
+        <v>1219.368</v>
       </c>
       <c r="G47">
         <v>81.2</v>
@@ -5141,37 +5141,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M47">
-        <v>281.2763880000001</v>
+        <v>287.5269744</v>
       </c>
       <c r="N47">
-        <v>-172.6355716734694</v>
+        <v>-178.8861580734694</v>
       </c>
       <c r="O47">
-        <v>-34.52711433469388</v>
+        <v>-35.77723161469388</v>
       </c>
       <c r="P47">
-        <v>-138.1084573387755</v>
+        <v>-143.1089264587755</v>
       </c>
       <c r="Q47">
-        <v>-119.7084573387755</v>
+        <v>-124.7089264587755</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1420302257770396</v>
+        <v>0.1438122669951329</v>
       </c>
       <c r="T47">
-        <v>1.82545182372207</v>
+        <v>1.859256487124331</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.07724844385198135</v>
+        <v>0.07556912985519915</v>
       </c>
       <c r="W47">
-        <v>0.2175848169397028</v>
+        <v>0.217980799180144</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3862422192599068</v>
+        <v>0.3778456492759957</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.177929791800238</v>
+        <v>0.1798297918002381</v>
       </c>
       <c r="C48">
-        <v>-91.40647095010195</v>
+        <v>-132.7533129603846</v>
       </c>
       <c r="D48">
-        <v>1046.761529049898</v>
+        <v>1031.922687039616</v>
       </c>
       <c r="E48">
-        <v>678.4680000000002</v>
+        <v>704.9760000000002</v>
       </c>
       <c r="F48">
-        <v>1219.368</v>
+        <v>1245.876</v>
       </c>
       <c r="G48">
         <v>81.2</v>
@@ -5223,37 +5223,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M48">
-        <v>287.5269744</v>
+        <v>293.7775608000001</v>
       </c>
       <c r="N48">
-        <v>-178.8861580734694</v>
+        <v>-185.1367444734694</v>
       </c>
       <c r="O48">
-        <v>-35.77723161469388</v>
+        <v>-37.02734889469389</v>
       </c>
       <c r="P48">
-        <v>-143.1089264587755</v>
+        <v>-148.1093955787755</v>
       </c>
       <c r="Q48">
-        <v>-124.7089264587755</v>
+        <v>-129.7093955787755</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1438122669951329</v>
+        <v>0.1456615550516449</v>
       </c>
       <c r="T48">
-        <v>1.859256487124331</v>
+        <v>1.894336798202149</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.07556912985519915</v>
+        <v>0.07396127602849277</v>
       </c>
       <c r="W48">
-        <v>0.217980799180144</v>
+        <v>0.2183599311124814</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3778456492759957</v>
+        <v>0.3698063801424639</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1798297918002381</v>
+        <v>0.181729791800238</v>
       </c>
       <c r="C49">
-        <v>-132.7533129603846</v>
+        <v>-173.6853261175343</v>
       </c>
       <c r="D49">
-        <v>1031.922687039616</v>
+        <v>1017.498673882466</v>
       </c>
       <c r="E49">
-        <v>704.9760000000002</v>
+        <v>731.4840000000003</v>
       </c>
       <c r="F49">
-        <v>1245.876</v>
+        <v>1272.384</v>
       </c>
       <c r="G49">
         <v>81.2</v>
@@ -5305,37 +5305,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M49">
-        <v>293.7775608000001</v>
+        <v>300.0281472000001</v>
       </c>
       <c r="N49">
-        <v>-185.1367444734694</v>
+        <v>-191.3873308734695</v>
       </c>
       <c r="O49">
-        <v>-37.02734889469389</v>
+        <v>-38.27746617469389</v>
       </c>
       <c r="P49">
-        <v>-148.1093955787755</v>
+        <v>-153.1098646987756</v>
       </c>
       <c r="Q49">
-        <v>-129.7093955787755</v>
+        <v>-134.7098646987756</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1456615550516449</v>
+        <v>0.1475819695718688</v>
       </c>
       <c r="T49">
-        <v>1.894336798202149</v>
+        <v>1.930766352013728</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.07396127602849277</v>
+        <v>0.0724204161112325</v>
       </c>
       <c r="W49">
-        <v>0.2183599311124814</v>
+        <v>0.2187232658809714</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3698063801424639</v>
+        <v>0.3621020805561626</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.181729791800238</v>
+        <v>0.183629791800238</v>
       </c>
       <c r="C50">
-        <v>-173.685326117534</v>
+        <v>-214.2196658161286</v>
       </c>
       <c r="D50">
-        <v>1017.498673882466</v>
+        <v>1003.472334183871</v>
       </c>
       <c r="E50">
-        <v>731.484</v>
+        <v>757.9920000000001</v>
       </c>
       <c r="F50">
-        <v>1272.384</v>
+        <v>1298.892</v>
       </c>
       <c r="G50">
         <v>81.2</v>
@@ -5387,37 +5387,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M50">
-        <v>300.0281472</v>
+        <v>306.2787336</v>
       </c>
       <c r="N50">
-        <v>-191.3873308734694</v>
+        <v>-197.6379172734694</v>
       </c>
       <c r="O50">
-        <v>-38.27746617469388</v>
+        <v>-39.52758345469388</v>
       </c>
       <c r="P50">
-        <v>-153.1098646987755</v>
+        <v>-158.1103338187755</v>
       </c>
       <c r="Q50">
-        <v>-134.7098646987755</v>
+        <v>-139.7103338187755</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1475819695718688</v>
+        <v>0.1495776944654348</v>
       </c>
       <c r="T50">
-        <v>1.930766352013728</v>
+        <v>1.968624515778703</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.07242041611123251</v>
+        <v>0.07094244843549308</v>
       </c>
       <c r="W50">
-        <v>0.2187232658809714</v>
+        <v>0.2190717706589108</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3621020805561627</v>
+        <v>0.3547122421774654</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.183629791800238</v>
+        <v>0.185529791800238</v>
       </c>
       <c r="C51">
-        <v>-214.2196658161286</v>
+        <v>-254.3725543569712</v>
       </c>
       <c r="D51">
-        <v>1003.472334183871</v>
+        <v>989.8274456430289</v>
       </c>
       <c r="E51">
-        <v>757.9920000000001</v>
+        <v>784.5000000000001</v>
       </c>
       <c r="F51">
-        <v>1298.892</v>
+        <v>1325.4</v>
       </c>
       <c r="G51">
         <v>81.2</v>
@@ -5469,37 +5469,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M51">
-        <v>306.2787336</v>
+        <v>312.52932</v>
       </c>
       <c r="N51">
-        <v>-197.6379172734694</v>
+        <v>-203.8885036734694</v>
       </c>
       <c r="O51">
-        <v>-39.52758345469388</v>
+        <v>-40.77770073469389</v>
       </c>
       <c r="P51">
-        <v>-158.1103338187755</v>
+        <v>-163.1108029387755</v>
       </c>
       <c r="Q51">
-        <v>-139.7103338187755</v>
+        <v>-144.7108029387755</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1495776944654348</v>
+        <v>0.1516532483547435</v>
       </c>
       <c r="T51">
-        <v>1.968624515778703</v>
+        <v>2.007997006094278</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.07094244843549308</v>
+        <v>0.06952359946678321</v>
       </c>
       <c r="W51">
-        <v>0.2190717706589108</v>
+        <v>0.2194063352457325</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3547122421774654</v>
+        <v>0.3476179973339161</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.185529791800238</v>
+        <v>0.187429791800238</v>
       </c>
       <c r="C52">
-        <v>-254.3725543569712</v>
+        <v>-294.1593435355526</v>
       </c>
       <c r="D52">
-        <v>989.8274456430289</v>
+        <v>976.5486564644475</v>
       </c>
       <c r="E52">
-        <v>784.5000000000001</v>
+        <v>811.0080000000002</v>
       </c>
       <c r="F52">
-        <v>1325.4</v>
+        <v>1351.908</v>
       </c>
       <c r="G52">
         <v>81.2</v>
@@ -5551,37 +5551,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M52">
-        <v>312.52932</v>
+        <v>318.7799064</v>
       </c>
       <c r="N52">
-        <v>-203.8885036734694</v>
+        <v>-210.1390900734694</v>
       </c>
       <c r="O52">
-        <v>-40.77770073469389</v>
+        <v>-42.02781801469388</v>
       </c>
       <c r="P52">
-        <v>-163.1108029387755</v>
+        <v>-168.1112720587755</v>
       </c>
       <c r="Q52">
-        <v>-144.7108029387755</v>
+        <v>-149.7112720587755</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1516532483547435</v>
+        <v>0.1538135187293301</v>
       </c>
       <c r="T52">
-        <v>2.007997006094278</v>
+        <v>2.048976536830895</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.06952359946678321</v>
+        <v>0.06816039163410119</v>
       </c>
       <c r="W52">
-        <v>0.2194063352457325</v>
+        <v>0.219727779652679</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3476179973339161</v>
+        <v>0.340801958170506</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.187429791800238</v>
+        <v>0.189329791800238</v>
       </c>
       <c r="C53">
-        <v>-294.1593435355526</v>
+        <v>-333.5945722593624</v>
       </c>
       <c r="D53">
-        <v>976.5486564644475</v>
+        <v>963.6214277406377</v>
       </c>
       <c r="E53">
-        <v>811.0080000000002</v>
+        <v>837.5160000000002</v>
       </c>
       <c r="F53">
-        <v>1351.908</v>
+        <v>1378.416</v>
       </c>
       <c r="G53">
         <v>81.2</v>
@@ -5633,37 +5633,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M53">
-        <v>318.7799064</v>
+        <v>325.0304928</v>
       </c>
       <c r="N53">
-        <v>-210.1390900734694</v>
+        <v>-216.3896764734694</v>
       </c>
       <c r="O53">
-        <v>-42.02781801469388</v>
+        <v>-43.27793529469389</v>
       </c>
       <c r="P53">
-        <v>-168.1112720587755</v>
+        <v>-173.1117411787755</v>
       </c>
       <c r="Q53">
-        <v>-149.7112720587755</v>
+        <v>-154.7117411787755</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1538135187293301</v>
+        <v>0.1560638003695245</v>
       </c>
       <c r="T53">
-        <v>2.048976536830895</v>
+        <v>2.091663548014873</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.06816039163410119</v>
+        <v>0.06684961487190694</v>
       </c>
       <c r="W53">
-        <v>0.219727779652679</v>
+        <v>0.2200368608132044</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.340801958170506</v>
+        <v>0.3342480743595347</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.189329791800238</v>
+        <v>0.1912297918002381</v>
       </c>
       <c r="C54">
-        <v>-333.5945722593624</v>
+        <v>-372.6920196486712</v>
       </c>
       <c r="D54">
-        <v>963.6214277406377</v>
+        <v>951.031980351329</v>
       </c>
       <c r="E54">
-        <v>837.5160000000002</v>
+        <v>864.0240000000002</v>
       </c>
       <c r="F54">
-        <v>1378.416</v>
+        <v>1404.924</v>
       </c>
       <c r="G54">
         <v>81.2</v>
@@ -5715,37 +5715,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M54">
-        <v>325.0304928</v>
+        <v>331.2810792000001</v>
       </c>
       <c r="N54">
-        <v>-216.3896764734694</v>
+        <v>-222.6402628734695</v>
       </c>
       <c r="O54">
-        <v>-43.27793529469389</v>
+        <v>-44.52805257469389</v>
       </c>
       <c r="P54">
-        <v>-173.1117411787755</v>
+        <v>-178.1122102987756</v>
       </c>
       <c r="Q54">
-        <v>-154.7117411787755</v>
+        <v>-159.7122102987755</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1560638003695245</v>
+        <v>0.1584098386752591</v>
       </c>
       <c r="T54">
-        <v>2.091663548014873</v>
+        <v>2.13616702775987</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.06684961487190694</v>
+        <v>0.06558830138375775</v>
       </c>
       <c r="W54">
-        <v>0.2200368608132044</v>
+        <v>0.2203342785337099</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3342480743595347</v>
+        <v>0.3279415069187888</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1912297918002381</v>
+        <v>0.193129791800238</v>
       </c>
       <c r="C55">
-        <v>-372.6920196486712</v>
+        <v>-411.4647540285141</v>
       </c>
       <c r="D55">
-        <v>951.031980351329</v>
+        <v>938.7672459714861</v>
       </c>
       <c r="E55">
-        <v>864.0240000000002</v>
+        <v>890.5320000000003</v>
       </c>
       <c r="F55">
-        <v>1404.924</v>
+        <v>1431.432</v>
       </c>
       <c r="G55">
         <v>81.2</v>
@@ -5797,37 +5797,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M55">
-        <v>331.2810792000001</v>
+        <v>337.5316656000001</v>
       </c>
       <c r="N55">
-        <v>-222.6402628734695</v>
+        <v>-228.8908492734694</v>
       </c>
       <c r="O55">
-        <v>-44.52805257469389</v>
+        <v>-45.77816985469389</v>
       </c>
       <c r="P55">
-        <v>-178.1122102987756</v>
+        <v>-183.1126794187755</v>
       </c>
       <c r="Q55">
-        <v>-159.7122102987755</v>
+        <v>-164.7126794187755</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1584098386752591</v>
+        <v>0.1608578786464603</v>
       </c>
       <c r="T55">
-        <v>2.13616702775987</v>
+        <v>2.182605441406823</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.06558830138375775</v>
+        <v>0.06437370320998446</v>
       </c>
       <c r="W55">
-        <v>0.2203342785337099</v>
+        <v>0.2206206807830857</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3279415069187888</v>
+        <v>0.3218685160499223</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.193129791800238</v>
+        <v>0.1950297918002381</v>
       </c>
       <c r="C56">
-        <v>-411.4647540285141</v>
+        <v>-449.9251781780669</v>
       </c>
       <c r="D56">
-        <v>938.7672459714861</v>
+        <v>926.8148218219334</v>
       </c>
       <c r="E56">
-        <v>890.5320000000003</v>
+        <v>917.0400000000003</v>
       </c>
       <c r="F56">
-        <v>1431.432</v>
+        <v>1457.94</v>
       </c>
       <c r="G56">
         <v>81.2</v>
@@ -5879,37 +5879,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M56">
-        <v>337.5316656000001</v>
+        <v>343.7822520000001</v>
       </c>
       <c r="N56">
-        <v>-228.8908492734694</v>
+        <v>-235.1414356734695</v>
       </c>
       <c r="O56">
-        <v>-45.77816985469389</v>
+        <v>-47.0282871346939</v>
       </c>
       <c r="P56">
-        <v>-183.1126794187755</v>
+        <v>-188.1131485387756</v>
       </c>
       <c r="Q56">
-        <v>-164.7126794187755</v>
+        <v>-169.7131485387756</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1608578786464603</v>
+        <v>0.1634147203941595</v>
       </c>
       <c r="T56">
-        <v>2.182605441406823</v>
+        <v>2.231107784549198</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.06437370320998446</v>
+        <v>0.06320327224253018</v>
       </c>
       <c r="W56">
-        <v>0.2206206807830857</v>
+        <v>0.2208966684052114</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3218685160499223</v>
+        <v>0.316016361212651</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1950297918002381</v>
+        <v>0.196929791800238</v>
       </c>
       <c r="C57">
-        <v>-449.9251781780669</v>
+        <v>-488.0850711667717</v>
       </c>
       <c r="D57">
-        <v>926.8148218219334</v>
+        <v>915.1629288332285</v>
       </c>
       <c r="E57">
-        <v>917.0400000000003</v>
+        <v>943.5480000000003</v>
       </c>
       <c r="F57">
-        <v>1457.94</v>
+        <v>1484.448</v>
       </c>
       <c r="G57">
         <v>81.2</v>
@@ -5961,37 +5961,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M57">
-        <v>343.7822520000001</v>
+        <v>350.0328384000001</v>
       </c>
       <c r="N57">
-        <v>-235.1414356734695</v>
+        <v>-241.3920220734695</v>
       </c>
       <c r="O57">
-        <v>-47.0282871346939</v>
+        <v>-48.2784044146939</v>
       </c>
       <c r="P57">
-        <v>-188.1131485387756</v>
+        <v>-193.1136176587756</v>
       </c>
       <c r="Q57">
-        <v>-169.7131485387756</v>
+        <v>-174.7136176587756</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1634147203941595</v>
+        <v>0.1660877822212995</v>
       </c>
       <c r="T57">
-        <v>2.231107784549198</v>
+        <v>2.281814779652588</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.06320327224253018</v>
+        <v>0.06207464238105642</v>
       </c>
       <c r="W57">
-        <v>0.2208966684052114</v>
+        <v>0.2211627993265469</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.316016361212651</v>
+        <v>0.3103732119052822</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.196929791800238</v>
+        <v>0.198829791800238</v>
       </c>
       <c r="C58">
-        <v>-488.0850711667717</v>
+        <v>-525.9556270738788</v>
       </c>
       <c r="D58">
-        <v>915.1629288332285</v>
+        <v>903.8003729261216</v>
       </c>
       <c r="E58">
-        <v>943.5480000000003</v>
+        <v>970.0560000000004</v>
       </c>
       <c r="F58">
-        <v>1484.448</v>
+        <v>1510.956</v>
       </c>
       <c r="G58">
         <v>81.2</v>
@@ -6043,37 +6043,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M58">
-        <v>350.0328384000001</v>
+        <v>356.2834248000001</v>
       </c>
       <c r="N58">
-        <v>-241.3920220734695</v>
+        <v>-247.6426084734695</v>
       </c>
       <c r="O58">
-        <v>-48.2784044146939</v>
+        <v>-49.52852169469389</v>
       </c>
       <c r="P58">
-        <v>-193.1136176587756</v>
+        <v>-198.1140867787756</v>
       </c>
       <c r="Q58">
-        <v>-174.7136176587756</v>
+        <v>-179.7140867787756</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1660877822212995</v>
+        <v>0.1688851725055157</v>
       </c>
       <c r="T58">
-        <v>2.281814779652588</v>
+        <v>2.334880239644509</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.06207464238105642</v>
+        <v>0.06098561356735369</v>
       </c>
       <c r="W58">
-        <v>0.2211627993265469</v>
+        <v>0.221419592320818</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3103732119052822</v>
+        <v>0.3049280678367685</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.198829791800238</v>
+        <v>0.2007297918002381</v>
       </c>
       <c r="C59">
-        <v>-525.9556270738788</v>
+        <v>-563.5474908589267</v>
       </c>
       <c r="D59">
-        <v>903.8003729261216</v>
+        <v>892.7165091410736</v>
       </c>
       <c r="E59">
-        <v>970.0560000000004</v>
+        <v>996.5640000000004</v>
       </c>
       <c r="F59">
-        <v>1510.956</v>
+        <v>1537.464</v>
       </c>
       <c r="G59">
         <v>81.2</v>
@@ -6125,37 +6125,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M59">
-        <v>356.2834248000001</v>
+        <v>362.5340112000001</v>
       </c>
       <c r="N59">
-        <v>-247.6426084734695</v>
+        <v>-253.8931948734695</v>
       </c>
       <c r="O59">
-        <v>-49.52852169469389</v>
+        <v>-50.77863897469391</v>
       </c>
       <c r="P59">
-        <v>-198.1140867787756</v>
+        <v>-203.1145558987756</v>
       </c>
       <c r="Q59">
-        <v>-179.7140867787756</v>
+        <v>-184.7145558987756</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1688851725055157</v>
+        <v>0.1718157718508852</v>
       </c>
       <c r="T59">
-        <v>2.334880239644509</v>
+        <v>2.390472626302711</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.06098561356735369</v>
+        <v>0.05993413747136483</v>
       </c>
       <c r="W59">
-        <v>0.221419592320818</v>
+        <v>0.2216675303842522</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3049280678367685</v>
+        <v>0.2996706873568241</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.200729791800238</v>
+        <v>0.202629791800238</v>
       </c>
       <c r="C60">
-        <v>-563.5474908589257</v>
+        <v>-600.8707916247943</v>
       </c>
       <c r="D60">
-        <v>892.7165091410742</v>
+        <v>881.9012083752057</v>
       </c>
       <c r="E60">
-        <v>996.564</v>
+        <v>1023.072</v>
       </c>
       <c r="F60">
-        <v>1537.464</v>
+        <v>1563.972</v>
       </c>
       <c r="G60">
         <v>81.2</v>
@@ -6207,37 +6207,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M60">
-        <v>362.5340112</v>
+        <v>368.7845976</v>
       </c>
       <c r="N60">
-        <v>-253.8931948734694</v>
+        <v>-260.1437812734694</v>
       </c>
       <c r="O60">
-        <v>-50.77863897469388</v>
+        <v>-52.02875625469387</v>
       </c>
       <c r="P60">
-        <v>-203.1145558987755</v>
+        <v>-208.1150250187755</v>
       </c>
       <c r="Q60">
-        <v>-184.7145558987755</v>
+        <v>-189.7150250187755</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1718157718508851</v>
+        <v>0.1748893272618823</v>
       </c>
       <c r="T60">
-        <v>2.390472626302711</v>
+        <v>2.448776836700338</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.05993413747136485</v>
+        <v>0.05891830463286714</v>
       </c>
       <c r="W60">
-        <v>0.2216675303842522</v>
+        <v>0.2219070637675699</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2996706873568242</v>
+        <v>0.2945915231643357</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.202629791800238</v>
+        <v>0.204529791800238</v>
       </c>
       <c r="C61">
-        <v>-600.8707916247943</v>
+        <v>-637.9351734917954</v>
       </c>
       <c r="D61">
-        <v>881.9012083752057</v>
+        <v>871.3448265082046</v>
       </c>
       <c r="E61">
-        <v>1023.072</v>
+        <v>1049.58</v>
       </c>
       <c r="F61">
-        <v>1563.972</v>
+        <v>1590.48</v>
       </c>
       <c r="G61">
         <v>81.2</v>
@@ -6289,37 +6289,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M61">
-        <v>368.7845976</v>
+        <v>375.035184</v>
       </c>
       <c r="N61">
-        <v>-260.1437812734694</v>
+        <v>-266.3943676734694</v>
       </c>
       <c r="O61">
-        <v>-52.02875625469387</v>
+        <v>-53.27887353469388</v>
       </c>
       <c r="P61">
-        <v>-208.1150250187755</v>
+        <v>-213.1154941387755</v>
       </c>
       <c r="Q61">
-        <v>-189.7150250187755</v>
+        <v>-194.7154941387755</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1748893272618823</v>
+        <v>0.1781165604434294</v>
       </c>
       <c r="T61">
-        <v>2.448776836700338</v>
+        <v>2.509996257617847</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.05891830463286714</v>
+        <v>0.05793633288898602</v>
       </c>
       <c r="W61">
-        <v>0.2219070637675699</v>
+        <v>0.2221386127047771</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2945915231643357</v>
+        <v>0.2896816644449302</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.204529791800238</v>
+        <v>0.206429791800238</v>
       </c>
       <c r="C62">
-        <v>-637.9351734917954</v>
+        <v>-674.7498242806131</v>
       </c>
       <c r="D62">
-        <v>871.3448265082046</v>
+        <v>861.0381757193869</v>
       </c>
       <c r="E62">
-        <v>1049.58</v>
+        <v>1076.088</v>
       </c>
       <c r="F62">
-        <v>1590.48</v>
+        <v>1616.988</v>
       </c>
       <c r="G62">
         <v>81.2</v>
@@ -6371,37 +6371,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M62">
-        <v>375.035184</v>
+        <v>381.2857704</v>
       </c>
       <c r="N62">
-        <v>-266.3943676734694</v>
+        <v>-272.6449540734694</v>
       </c>
       <c r="O62">
-        <v>-53.27887353469388</v>
+        <v>-54.52899081469388</v>
       </c>
       <c r="P62">
-        <v>-213.1154941387755</v>
+        <v>-218.1159632587755</v>
       </c>
       <c r="Q62">
-        <v>-194.7154941387755</v>
+        <v>-199.7159632587755</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1781165604434294</v>
+        <v>0.1815092927624917</v>
       </c>
       <c r="T62">
-        <v>2.509996257617847</v>
+        <v>2.574355136018304</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.05793633288898602</v>
+        <v>0.05698655693998625</v>
       </c>
       <c r="W62">
-        <v>0.2221386127047771</v>
+        <v>0.2223625698735513</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2896816644449302</v>
+        <v>0.2849327846999312</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.206429791800238</v>
+        <v>0.208329791800238</v>
       </c>
       <c r="C63">
-        <v>-674.7498242806131</v>
+        <v>-711.3235021833915</v>
       </c>
       <c r="D63">
-        <v>861.0381757193869</v>
+        <v>850.9724978166086</v>
       </c>
       <c r="E63">
-        <v>1076.088</v>
+        <v>1102.596</v>
       </c>
       <c r="F63">
-        <v>1616.988</v>
+        <v>1643.496</v>
       </c>
       <c r="G63">
         <v>81.2</v>
@@ -6453,37 +6453,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M63">
-        <v>381.2857704</v>
+        <v>387.5363568</v>
       </c>
       <c r="N63">
-        <v>-272.6449540734694</v>
+        <v>-278.8955404734694</v>
       </c>
       <c r="O63">
-        <v>-54.52899081469388</v>
+        <v>-55.77910809469388</v>
       </c>
       <c r="P63">
-        <v>-218.1159632587755</v>
+        <v>-223.1164323787755</v>
       </c>
       <c r="Q63">
-        <v>-199.7159632587755</v>
+        <v>-204.7164323787755</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1815092927624917</v>
+        <v>0.185080589940452</v>
       </c>
       <c r="T63">
-        <v>2.574355136018304</v>
+        <v>2.64210132380826</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.05698655693998625</v>
+        <v>0.05606741892482518</v>
       </c>
       <c r="W63">
-        <v>0.2223625698735513</v>
+        <v>0.2225793026175262</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2849327846999312</v>
+        <v>0.2803370946241259</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.208329791800238</v>
+        <v>0.210229791800238</v>
       </c>
       <c r="C64">
-        <v>-711.3235021833915</v>
+        <v>-747.6645605857024</v>
       </c>
       <c r="D64">
-        <v>850.9724978166086</v>
+        <v>841.1394394142977</v>
       </c>
       <c r="E64">
-        <v>1102.596</v>
+        <v>1129.104</v>
       </c>
       <c r="F64">
-        <v>1643.496</v>
+        <v>1670.004</v>
       </c>
       <c r="G64">
         <v>81.2</v>
@@ -6535,37 +6535,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M64">
-        <v>387.5363568</v>
+        <v>393.7869432000001</v>
       </c>
       <c r="N64">
-        <v>-278.8955404734694</v>
+        <v>-285.1461268734694</v>
       </c>
       <c r="O64">
-        <v>-55.77910809469388</v>
+        <v>-57.02922537469389</v>
       </c>
       <c r="P64">
-        <v>-223.1164323787755</v>
+        <v>-228.1169014987755</v>
       </c>
       <c r="Q64">
-        <v>-204.7164323787755</v>
+        <v>-209.7169014987755</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.185080589940452</v>
+        <v>0.1888449302091129</v>
       </c>
       <c r="T64">
-        <v>2.64210132380826</v>
+        <v>2.713509467694969</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.05606741892482518</v>
+        <v>0.05517745989427239</v>
       </c>
       <c r="W64">
-        <v>0.2225793026175262</v>
+        <v>0.2227891549569306</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2803370946241259</v>
+        <v>0.275887299471362</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.210229791800238</v>
+        <v>0.212129791800238</v>
       </c>
       <c r="C65">
-        <v>-747.6645605857024</v>
+        <v>-783.7809711872535</v>
       </c>
       <c r="D65">
-        <v>841.1394394142977</v>
+        <v>831.5310288127466</v>
       </c>
       <c r="E65">
-        <v>1129.104</v>
+        <v>1155.612</v>
       </c>
       <c r="F65">
-        <v>1670.004</v>
+        <v>1696.512</v>
       </c>
       <c r="G65">
         <v>81.2</v>
@@ -6617,37 +6617,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M65">
-        <v>393.7869432000001</v>
+        <v>400.0375296000001</v>
       </c>
       <c r="N65">
-        <v>-285.1461268734694</v>
+        <v>-291.3967132734695</v>
       </c>
       <c r="O65">
-        <v>-57.02922537469389</v>
+        <v>-58.27934265469389</v>
       </c>
       <c r="P65">
-        <v>-228.1169014987755</v>
+        <v>-233.1173706187756</v>
       </c>
       <c r="Q65">
-        <v>-209.7169014987755</v>
+        <v>-214.7173706187756</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1888449302091129</v>
+        <v>0.1928184004926994</v>
       </c>
       <c r="T65">
-        <v>2.713509467694969</v>
+        <v>2.788884730686497</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.05517745989427239</v>
+        <v>0.05431531208342438</v>
       </c>
       <c r="W65">
-        <v>0.2227891549569306</v>
+        <v>0.2229924494107285</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.275887299471362</v>
+        <v>0.271576560417122</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.212129791800238</v>
+        <v>0.214029791800238</v>
       </c>
       <c r="C66">
-        <v>-783.7809711872535</v>
+        <v>-819.680345555833</v>
       </c>
       <c r="D66">
-        <v>831.5310288127466</v>
+        <v>822.1396544441671</v>
       </c>
       <c r="E66">
-        <v>1155.612</v>
+        <v>1182.12</v>
       </c>
       <c r="F66">
-        <v>1696.512</v>
+        <v>1723.02</v>
       </c>
       <c r="G66">
         <v>81.2</v>
@@ -6699,37 +6699,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M66">
-        <v>400.0375296000001</v>
+        <v>406.2881160000001</v>
       </c>
       <c r="N66">
-        <v>-291.3967132734695</v>
+        <v>-297.6472996734694</v>
       </c>
       <c r="O66">
-        <v>-58.27934265469389</v>
+        <v>-59.52945993469389</v>
       </c>
       <c r="P66">
-        <v>-233.1173706187756</v>
+        <v>-238.1178397387756</v>
       </c>
       <c r="Q66">
-        <v>-214.7173706187756</v>
+        <v>-219.7178397387756</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1928184004926994</v>
+        <v>0.1970189262210622</v>
       </c>
       <c r="T66">
-        <v>2.788884730686497</v>
+        <v>2.868567151563254</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.05431531208342438</v>
+        <v>0.05347969189752555</v>
       </c>
       <c r="W66">
-        <v>0.2229924494107285</v>
+        <v>0.2231894886505635</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.271576560417122</v>
+        <v>0.2673984594876277</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.214029791800238</v>
+        <v>0.215929791800238</v>
       </c>
       <c r="C67">
-        <v>-819.680345555833</v>
+        <v>-855.3699552369762</v>
       </c>
       <c r="D67">
-        <v>822.1396544441671</v>
+        <v>812.958044763024</v>
       </c>
       <c r="E67">
-        <v>1182.12</v>
+        <v>1208.628</v>
       </c>
       <c r="F67">
-        <v>1723.02</v>
+        <v>1749.528</v>
       </c>
       <c r="G67">
         <v>81.2</v>
@@ -6781,37 +6781,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M67">
-        <v>406.2881160000001</v>
+        <v>412.5387024000001</v>
       </c>
       <c r="N67">
-        <v>-297.6472996734694</v>
+        <v>-303.8978860734695</v>
       </c>
       <c r="O67">
-        <v>-59.52945993469389</v>
+        <v>-60.77957721469389</v>
       </c>
       <c r="P67">
-        <v>-238.1178397387756</v>
+        <v>-243.1183088587756</v>
       </c>
       <c r="Q67">
-        <v>-219.7178397387756</v>
+        <v>-224.7183088587756</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1970189262210622</v>
+        <v>0.2014665416981523</v>
       </c>
       <c r="T67">
-        <v>2.868567151563254</v>
+        <v>2.952936773668055</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.05347969189752555</v>
+        <v>0.05266939353544182</v>
       </c>
       <c r="W67">
-        <v>0.2231894886505635</v>
+        <v>0.2233805570043428</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2673984594876277</v>
+        <v>0.2633469676772091</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.215929791800238</v>
+        <v>0.217829791800238</v>
       </c>
       <c r="C68">
-        <v>-855.3699552369762</v>
+        <v>-890.856750531011</v>
       </c>
       <c r="D68">
-        <v>812.958044763024</v>
+        <v>803.9792494689892</v>
       </c>
       <c r="E68">
-        <v>1208.628</v>
+        <v>1235.136</v>
       </c>
       <c r="F68">
-        <v>1749.528</v>
+        <v>1776.036</v>
       </c>
       <c r="G68">
         <v>81.2</v>
@@ -6863,37 +6863,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M68">
-        <v>412.5387024000001</v>
+        <v>418.7892888000001</v>
       </c>
       <c r="N68">
-        <v>-303.8978860734695</v>
+        <v>-310.1484724734694</v>
       </c>
       <c r="O68">
-        <v>-60.77957721469389</v>
+        <v>-62.02969449469389</v>
       </c>
       <c r="P68">
-        <v>-243.1183088587756</v>
+        <v>-248.1187779787755</v>
       </c>
       <c r="Q68">
-        <v>-224.7183088587756</v>
+        <v>-229.7187779787755</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2014665416981523</v>
+        <v>0.2061837096283993</v>
       </c>
       <c r="T68">
-        <v>2.952936773668055</v>
+        <v>3.042419706203451</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.05266939353544182</v>
+        <v>0.05188328318416657</v>
       </c>
       <c r="W68">
-        <v>0.2233805570043428</v>
+        <v>0.2235659218251735</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2633469676772091</v>
+        <v>0.2594164159208329</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.217829791800238</v>
+        <v>0.2197297918002381</v>
       </c>
       <c r="C69">
-        <v>-890.856750531011</v>
+        <v>-926.1473780393881</v>
       </c>
       <c r="D69">
-        <v>803.9792494689892</v>
+        <v>795.1966219606122</v>
       </c>
       <c r="E69">
-        <v>1235.136</v>
+        <v>1261.644</v>
       </c>
       <c r="F69">
-        <v>1776.036</v>
+        <v>1802.544</v>
       </c>
       <c r="G69">
         <v>81.2</v>
@@ -6945,37 +6945,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M69">
-        <v>418.7892888000001</v>
+        <v>425.0398752000001</v>
       </c>
       <c r="N69">
-        <v>-310.1484724734694</v>
+        <v>-316.3990588734695</v>
       </c>
       <c r="O69">
-        <v>-62.02969449469389</v>
+        <v>-63.2798117746939</v>
       </c>
       <c r="P69">
-        <v>-248.1187779787755</v>
+        <v>-253.1192470987756</v>
       </c>
       <c r="Q69">
-        <v>-229.7187779787755</v>
+        <v>-234.7192470987756</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2061837096283993</v>
+        <v>0.2111957005542868</v>
       </c>
       <c r="T69">
-        <v>3.042419706203451</v>
+        <v>3.137495322022309</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.05188328318416657</v>
+        <v>0.05112029372557589</v>
       </c>
       <c r="W69">
-        <v>0.2235659218251735</v>
+        <v>0.2237458347395092</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2594164159208329</v>
+        <v>0.2556014686278795</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2197297918002381</v>
+        <v>0.2216297918002381</v>
       </c>
       <c r="C70">
-        <v>-926.1473780393881</v>
+        <v>-961.2481970733874</v>
       </c>
       <c r="D70">
-        <v>795.1966219606122</v>
+        <v>786.603802926613</v>
       </c>
       <c r="E70">
-        <v>1261.644</v>
+        <v>1288.152</v>
       </c>
       <c r="F70">
-        <v>1802.544</v>
+        <v>1829.052</v>
       </c>
       <c r="G70">
         <v>81.2</v>
@@ -7027,37 +7027,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M70">
-        <v>425.0398752000001</v>
+        <v>431.2904616000001</v>
       </c>
       <c r="N70">
-        <v>-316.3990588734695</v>
+        <v>-322.6496452734695</v>
       </c>
       <c r="O70">
-        <v>-63.2798117746939</v>
+        <v>-64.52992905469391</v>
       </c>
       <c r="P70">
-        <v>-253.1192470987756</v>
+        <v>-258.1197162187756</v>
       </c>
       <c r="Q70">
-        <v>-234.7192470987756</v>
+        <v>-239.7197162187756</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2111957005542868</v>
+        <v>0.2165310457334574</v>
       </c>
       <c r="T70">
-        <v>3.137495322022309</v>
+        <v>3.238704848539158</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.05112029372557589</v>
+        <v>0.05037941990346609</v>
       </c>
       <c r="W70">
-        <v>0.2237458347395092</v>
+        <v>0.2239205327867627</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2556014686278795</v>
+        <v>0.2518970995173304</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2216297918002381</v>
+        <v>0.223529791800238</v>
       </c>
       <c r="C71">
-        <v>-961.2481970733874</v>
+        <v>-996.1652950103294</v>
       </c>
       <c r="D71">
-        <v>786.603802926613</v>
+        <v>778.194704989671</v>
       </c>
       <c r="E71">
-        <v>1288.152</v>
+        <v>1314.66</v>
       </c>
       <c r="F71">
-        <v>1829.052</v>
+        <v>1855.56</v>
       </c>
       <c r="G71">
         <v>81.2</v>
@@ -7109,37 +7109,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M71">
-        <v>431.2904616000001</v>
+        <v>437.5410480000001</v>
       </c>
       <c r="N71">
-        <v>-322.6496452734695</v>
+        <v>-328.9002316734695</v>
       </c>
       <c r="O71">
-        <v>-64.52992905469391</v>
+        <v>-65.78004633469389</v>
       </c>
       <c r="P71">
-        <v>-258.1197162187756</v>
+        <v>-263.1201853387756</v>
       </c>
       <c r="Q71">
-        <v>-239.7197162187756</v>
+        <v>-244.7201853387756</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2165310457334574</v>
+        <v>0.2222220805912393</v>
       </c>
       <c r="T71">
-        <v>3.238704848539158</v>
+        <v>3.346661676823797</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.05037941990346609</v>
+        <v>0.04965971390484514</v>
       </c>
       <c r="W71">
-        <v>0.2239205327867627</v>
+        <v>0.2240902394612375</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2518970995173304</v>
+        <v>0.2482985695242258</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.223529791800238</v>
+        <v>0.225429791800238</v>
       </c>
       <c r="C72">
-        <v>-996.1652950103294</v>
+        <v>-1030.904501675227</v>
       </c>
       <c r="D72">
-        <v>778.194704989671</v>
+        <v>769.9634983247728</v>
       </c>
       <c r="E72">
-        <v>1314.66</v>
+        <v>1341.168000000001</v>
       </c>
       <c r="F72">
-        <v>1855.56</v>
+        <v>1882.068</v>
       </c>
       <c r="G72">
         <v>81.2</v>
@@ -7191,37 +7191,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M72">
-        <v>437.5410480000001</v>
+        <v>443.7916344000001</v>
       </c>
       <c r="N72">
-        <v>-328.9002316734695</v>
+        <v>-335.1508180734695</v>
       </c>
       <c r="O72">
-        <v>-65.78004633469389</v>
+        <v>-67.0301636146939</v>
       </c>
       <c r="P72">
-        <v>-263.1201853387756</v>
+        <v>-268.1206544587756</v>
       </c>
       <c r="Q72">
-        <v>-244.7201853387756</v>
+        <v>-249.7206544587756</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2222220805912393</v>
+        <v>0.2283056006116268</v>
       </c>
       <c r="T72">
-        <v>3.346661676823797</v>
+        <v>3.462063803610824</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.04965971390484514</v>
+        <v>0.04896028131463606</v>
       </c>
       <c r="W72">
-        <v>0.2240902394612375</v>
+        <v>0.2242551656660088</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2482985695242258</v>
+        <v>0.2448014065731803</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.225429791800238</v>
+        <v>0.227329791800238</v>
       </c>
       <c r="C73">
-        <v>-1030.904501675227</v>
+        <v>-1065.471402819272</v>
       </c>
       <c r="D73">
-        <v>769.9634983247728</v>
+        <v>761.9045971807283</v>
       </c>
       <c r="E73">
-        <v>1341.168</v>
+        <v>1367.676</v>
       </c>
       <c r="F73">
-        <v>1882.068</v>
+        <v>1908.576</v>
       </c>
       <c r="G73">
         <v>81.2</v>
@@ -7273,37 +7273,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M73">
-        <v>443.7916344</v>
+        <v>450.0422208</v>
       </c>
       <c r="N73">
-        <v>-335.1508180734694</v>
+        <v>-341.4014044734694</v>
       </c>
       <c r="O73">
-        <v>-67.03016361469388</v>
+        <v>-68.28028089469387</v>
       </c>
       <c r="P73">
-        <v>-268.1206544587755</v>
+        <v>-273.1211235787755</v>
       </c>
       <c r="Q73">
-        <v>-249.7206544587755</v>
+        <v>-254.7211235787755</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2283056006116268</v>
+        <v>0.2348236577763277</v>
       </c>
       <c r="T73">
-        <v>3.462063803610823</v>
+        <v>3.585708939454067</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.04896028131463607</v>
+        <v>0.04828027740748835</v>
       </c>
       <c r="W73">
-        <v>0.2242551656660088</v>
+        <v>0.2244155105873143</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2448014065731804</v>
+        <v>0.2414013870374417</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.227329791800238</v>
+        <v>0.229229791800238</v>
       </c>
       <c r="C74">
-        <v>-1065.471402819272</v>
+        <v>-1099.871352760641</v>
       </c>
       <c r="D74">
-        <v>761.9045971807283</v>
+        <v>754.0126472393586</v>
       </c>
       <c r="E74">
-        <v>1367.676</v>
+        <v>1394.184</v>
       </c>
       <c r="F74">
-        <v>1908.576</v>
+        <v>1935.084</v>
       </c>
       <c r="G74">
         <v>81.2</v>
@@ -7355,37 +7355,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M74">
-        <v>450.0422208</v>
+        <v>456.2928072</v>
       </c>
       <c r="N74">
-        <v>-341.4014044734694</v>
+        <v>-347.6519908734694</v>
       </c>
       <c r="O74">
-        <v>-68.28028089469387</v>
+        <v>-69.53039817469389</v>
       </c>
       <c r="P74">
-        <v>-273.1211235787755</v>
+        <v>-278.1215926987755</v>
       </c>
       <c r="Q74">
-        <v>-254.7211235787755</v>
+        <v>-259.7215926987756</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2348236577763277</v>
+        <v>0.2418245339902658</v>
       </c>
       <c r="T74">
-        <v>3.585708939454067</v>
+        <v>3.718512974248661</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.04828027740748835</v>
+        <v>0.04761890374437207</v>
       </c>
       <c r="W74">
-        <v>0.2244155105873143</v>
+        <v>0.2245714624970771</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2414013870374417</v>
+        <v>0.2380945187218604</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.229229791800238</v>
+        <v>0.231129791800238</v>
       </c>
       <c r="C75">
-        <v>-1099.871352760641</v>
+        <v>-1134.109486247755</v>
       </c>
       <c r="D75">
-        <v>754.0126472393586</v>
+        <v>746.282513752245</v>
       </c>
       <c r="E75">
-        <v>1394.184</v>
+        <v>1420.692</v>
       </c>
       <c r="F75">
-        <v>1935.084</v>
+        <v>1961.592</v>
       </c>
       <c r="G75">
         <v>81.2</v>
@@ -7437,37 +7437,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M75">
-        <v>456.2928072</v>
+        <v>462.5433936000001</v>
       </c>
       <c r="N75">
-        <v>-347.6519908734694</v>
+        <v>-353.9025772734694</v>
       </c>
       <c r="O75">
-        <v>-69.53039817469389</v>
+        <v>-70.78051545469388</v>
       </c>
       <c r="P75">
-        <v>-278.1215926987755</v>
+        <v>-283.1220618187755</v>
       </c>
       <c r="Q75">
-        <v>-259.7215926987756</v>
+        <v>-264.7220618187755</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2418245339902658</v>
+        <v>0.2493639391437376</v>
       </c>
       <c r="T75">
-        <v>3.718512974248661</v>
+        <v>3.861532704027456</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.04761890374437207</v>
+        <v>0.04697540504512379</v>
       </c>
       <c r="W75">
-        <v>0.2245714624970771</v>
+        <v>0.2247231994903598</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2380945187218604</v>
+        <v>0.234877025225619</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.231129791800238</v>
+        <v>0.233029791800238</v>
       </c>
       <c r="C76">
-        <v>-1134.109486247755</v>
+        <v>-1168.190729600191</v>
       </c>
       <c r="D76">
-        <v>746.282513752245</v>
+        <v>738.7092703998086</v>
       </c>
       <c r="E76">
-        <v>1420.692</v>
+        <v>1447.2</v>
       </c>
       <c r="F76">
-        <v>1961.592</v>
+        <v>1988.1</v>
       </c>
       <c r="G76">
         <v>81.2</v>
@@ -7519,37 +7519,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M76">
-        <v>462.5433936000001</v>
+        <v>468.79398</v>
       </c>
       <c r="N76">
-        <v>-353.9025772734694</v>
+        <v>-360.1531636734694</v>
       </c>
       <c r="O76">
-        <v>-70.78051545469388</v>
+        <v>-72.03063273469388</v>
       </c>
       <c r="P76">
-        <v>-283.1220618187755</v>
+        <v>-288.1225309387755</v>
       </c>
       <c r="Q76">
-        <v>-264.7220618187755</v>
+        <v>-269.7225309387755</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2493639391437376</v>
+        <v>0.257506496709487</v>
       </c>
       <c r="T76">
-        <v>3.861532704027456</v>
+        <v>4.015994012188554</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.04697540504512379</v>
+        <v>0.04634906631118881</v>
       </c>
       <c r="W76">
-        <v>0.2247231994903598</v>
+        <v>0.2248708901638217</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.234877025225619</v>
+        <v>0.2317453315559441</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.233029791800238</v>
+        <v>0.234929791800238</v>
       </c>
       <c r="C77">
-        <v>-1168.190729600191</v>
+        <v>-1202.119811178085</v>
       </c>
       <c r="D77">
-        <v>738.7092703998086</v>
+        <v>731.288188821915</v>
       </c>
       <c r="E77">
-        <v>1447.2</v>
+        <v>1473.708</v>
       </c>
       <c r="F77">
-        <v>1988.1</v>
+        <v>2014.608</v>
       </c>
       <c r="G77">
         <v>81.2</v>
@@ -7601,37 +7601,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M77">
-        <v>468.79398</v>
+        <v>475.0445664000001</v>
       </c>
       <c r="N77">
-        <v>-360.1531636734694</v>
+        <v>-366.4037500734694</v>
       </c>
       <c r="O77">
-        <v>-72.03063273469388</v>
+        <v>-73.28075001469389</v>
       </c>
       <c r="P77">
-        <v>-288.1225309387755</v>
+        <v>-293.1230000587756</v>
       </c>
       <c r="Q77">
-        <v>-269.7225309387755</v>
+        <v>-274.7230000587756</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.257506496709487</v>
+        <v>0.266327600739049</v>
       </c>
       <c r="T77">
-        <v>4.015994012188554</v>
+        <v>4.183327096029745</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.04634906631118881</v>
+        <v>0.04573921017551527</v>
       </c>
       <c r="W77">
-        <v>0.2248708901638217</v>
+        <v>0.2250146942406135</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2317453315559441</v>
+        <v>0.2286960508775764</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.234929791800238</v>
+        <v>0.236829791800238</v>
       </c>
       <c r="C78">
-        <v>-1202.119811178085</v>
+        <v>-1235.901271226739</v>
       </c>
       <c r="D78">
-        <v>731.288188821915</v>
+        <v>724.0147287732614</v>
       </c>
       <c r="E78">
-        <v>1473.708</v>
+        <v>1500.216</v>
       </c>
       <c r="F78">
-        <v>2014.608</v>
+        <v>2041.116</v>
       </c>
       <c r="G78">
         <v>81.2</v>
@@ -7683,37 +7683,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M78">
-        <v>475.0445664000001</v>
+        <v>481.2951528000001</v>
       </c>
       <c r="N78">
-        <v>-366.4037500734694</v>
+        <v>-372.6543364734695</v>
       </c>
       <c r="O78">
-        <v>-73.28075001469389</v>
+        <v>-74.53086729469389</v>
       </c>
       <c r="P78">
-        <v>-293.1230000587756</v>
+        <v>-298.1234691787756</v>
       </c>
       <c r="Q78">
-        <v>-274.7230000587756</v>
+        <v>-279.7234691787755</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.266327600739049</v>
+        <v>0.2759157572929207</v>
       </c>
       <c r="T78">
-        <v>4.183327096029745</v>
+        <v>4.365210882813646</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.04573921017551527</v>
+        <v>0.04514519445895013</v>
       </c>
       <c r="W78">
-        <v>0.2250146942406135</v>
+        <v>0.2251547631465796</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2286960508775764</v>
+        <v>0.2257259722947507</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.236829791800238</v>
+        <v>0.238729791800238</v>
       </c>
       <c r="C79">
-        <v>-1235.901271226739</v>
+        <v>-1269.539471139532</v>
       </c>
       <c r="D79">
-        <v>724.0147287732614</v>
+        <v>716.8845288604683</v>
       </c>
       <c r="E79">
-        <v>1500.216</v>
+        <v>1526.724</v>
       </c>
       <c r="F79">
-        <v>2041.116</v>
+        <v>2067.624</v>
       </c>
       <c r="G79">
         <v>81.2</v>
@@ -7765,37 +7765,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M79">
-        <v>481.2951528000001</v>
+        <v>487.5457392000001</v>
       </c>
       <c r="N79">
-        <v>-372.6543364734695</v>
+        <v>-378.9049228734694</v>
       </c>
       <c r="O79">
-        <v>-74.53086729469389</v>
+        <v>-75.78098457469389</v>
       </c>
       <c r="P79">
-        <v>-298.1234691787756</v>
+        <v>-303.1239382987756</v>
       </c>
       <c r="Q79">
-        <v>-279.7234691787755</v>
+        <v>-284.7239382987756</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2759157572929207</v>
+        <v>0.286375564442599</v>
       </c>
       <c r="T79">
-        <v>4.365210882813646</v>
+        <v>4.563629559305177</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.04514519445895013</v>
+        <v>0.04456640991460462</v>
       </c>
       <c r="W79">
-        <v>0.2251547631465796</v>
+        <v>0.2252912405421363</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2257259722947507</v>
+        <v>0.2228320495730232</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.238729791800238</v>
+        <v>0.240629791800238</v>
       </c>
       <c r="C80">
-        <v>-1269.539471139532</v>
+        <v>-1303.038602178831</v>
       </c>
       <c r="D80">
-        <v>716.8845288604683</v>
+        <v>709.8933978211686</v>
       </c>
       <c r="E80">
-        <v>1526.724</v>
+        <v>1553.232</v>
       </c>
       <c r="F80">
-        <v>2067.624</v>
+        <v>2094.132</v>
       </c>
       <c r="G80">
         <v>81.2</v>
@@ -7847,37 +7847,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M80">
-        <v>487.5457392000001</v>
+        <v>493.7963256</v>
       </c>
       <c r="N80">
-        <v>-378.9049228734694</v>
+        <v>-385.1555092734694</v>
       </c>
       <c r="O80">
-        <v>-75.78098457469389</v>
+        <v>-77.03110185469389</v>
       </c>
       <c r="P80">
-        <v>-303.1239382987756</v>
+        <v>-308.1244074187755</v>
       </c>
       <c r="Q80">
-        <v>-284.7239382987756</v>
+        <v>-289.7244074187755</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.286375564442599</v>
+        <v>0.2978315437017703</v>
       </c>
       <c r="T80">
-        <v>4.563629559305177</v>
+        <v>4.780945252605423</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.04456640991460462</v>
+        <v>0.04400227814353368</v>
       </c>
       <c r="W80">
-        <v>0.2252912405421363</v>
+        <v>0.2254242628137548</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2228320495730232</v>
+        <v>0.2200113907176684</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.240629791800238</v>
+        <v>0.242529791800238</v>
       </c>
       <c r="C81">
-        <v>-1303.038602178831</v>
+        <v>-1336.402693691549</v>
       </c>
       <c r="D81">
-        <v>709.8933978211686</v>
+        <v>703.0373063084514</v>
       </c>
       <c r="E81">
-        <v>1553.232</v>
+        <v>1579.74</v>
       </c>
       <c r="F81">
-        <v>2094.132</v>
+        <v>2120.64</v>
       </c>
       <c r="G81">
         <v>81.2</v>
@@ -7929,37 +7929,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M81">
-        <v>493.7963256</v>
+        <v>500.0469120000001</v>
       </c>
       <c r="N81">
-        <v>-385.1555092734694</v>
+        <v>-391.4060956734695</v>
       </c>
       <c r="O81">
-        <v>-77.03110185469389</v>
+        <v>-78.2812191346939</v>
       </c>
       <c r="P81">
-        <v>-308.1244074187755</v>
+        <v>-313.1248765387755</v>
       </c>
       <c r="Q81">
-        <v>-289.7244074187755</v>
+        <v>-294.7248765387756</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2978315437017703</v>
+        <v>0.3104331208868589</v>
       </c>
       <c r="T81">
-        <v>4.780945252605423</v>
+        <v>5.019992515235694</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.04400227814353368</v>
+        <v>0.04345224966673951</v>
       </c>
       <c r="W81">
-        <v>0.2254242628137548</v>
+        <v>0.2255539595285828</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2200113907176684</v>
+        <v>0.2172612483336975</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.242529791800238</v>
+        <v>0.244429791800238</v>
       </c>
       <c r="C82">
-        <v>-1336.402693691549</v>
+        <v>-1369.635620853177</v>
       </c>
       <c r="D82">
-        <v>703.0373063084514</v>
+        <v>696.3123791468229</v>
       </c>
       <c r="E82">
-        <v>1579.74</v>
+        <v>1606.248</v>
       </c>
       <c r="F82">
-        <v>2120.64</v>
+        <v>2147.148</v>
       </c>
       <c r="G82">
         <v>81.2</v>
@@ -8011,37 +8011,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M82">
-        <v>500.0469120000001</v>
+        <v>506.2974984000001</v>
       </c>
       <c r="N82">
-        <v>-391.4060956734695</v>
+        <v>-397.6566820734694</v>
       </c>
       <c r="O82">
-        <v>-78.2812191346939</v>
+        <v>-79.5313364146939</v>
       </c>
       <c r="P82">
-        <v>-313.1248765387755</v>
+        <v>-318.1253456587755</v>
       </c>
       <c r="Q82">
-        <v>-294.7248765387756</v>
+        <v>-299.7253456587755</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3104331208868589</v>
+        <v>0.3243611798809041</v>
       </c>
       <c r="T82">
-        <v>5.019992515235694</v>
+        <v>5.28420264761652</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.04345224966673951</v>
+        <v>0.04291580213998964</v>
       </c>
       <c r="W82">
-        <v>0.2255539595285828</v>
+        <v>0.2256804538553904</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2172612483336975</v>
+        <v>0.2145790106999482</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.244429791800238</v>
+        <v>0.2463297918002381</v>
       </c>
       <c r="C83">
-        <v>-1369.635620853177</v>
+        <v>-1402.741111971589</v>
       </c>
       <c r="D83">
-        <v>696.3123791468229</v>
+        <v>689.7148880284115</v>
       </c>
       <c r="E83">
-        <v>1606.248</v>
+        <v>1632.756</v>
       </c>
       <c r="F83">
-        <v>2147.148</v>
+        <v>2173.656</v>
       </c>
       <c r="G83">
         <v>81.2</v>
@@ -8093,37 +8093,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M83">
-        <v>506.2974984000001</v>
+        <v>512.5480848000001</v>
       </c>
       <c r="N83">
-        <v>-397.6566820734694</v>
+        <v>-403.9072684734695</v>
       </c>
       <c r="O83">
-        <v>-79.5313364146939</v>
+        <v>-80.78145369469389</v>
       </c>
       <c r="P83">
-        <v>-318.1253456587755</v>
+        <v>-323.1258147787756</v>
       </c>
       <c r="Q83">
-        <v>-299.7253456587755</v>
+        <v>-304.7258147787755</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3243611798809041</v>
+        <v>0.3398368009853988</v>
       </c>
       <c r="T83">
-        <v>5.28420264761652</v>
+        <v>5.577769461372994</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.04291580213998964</v>
+        <v>0.04239243869925806</v>
       </c>
       <c r="W83">
-        <v>0.2256804538553904</v>
+        <v>0.225803862954715</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2145790106999482</v>
+        <v>0.2119621934962903</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2463297918002381</v>
+        <v>0.248229791800238</v>
       </c>
       <c r="C84">
-        <v>-1402.741111971589</v>
+        <v>-1435.722755379508</v>
       </c>
       <c r="D84">
-        <v>689.7148880284115</v>
+        <v>683.2412446204926</v>
       </c>
       <c r="E84">
-        <v>1632.756</v>
+        <v>1659.264</v>
       </c>
       <c r="F84">
-        <v>2173.656</v>
+        <v>2200.164</v>
       </c>
       <c r="G84">
         <v>81.2</v>
@@ -8175,37 +8175,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M84">
-        <v>512.5480848000001</v>
+        <v>518.7986712000001</v>
       </c>
       <c r="N84">
-        <v>-403.9072684734695</v>
+        <v>-410.1578548734694</v>
       </c>
       <c r="O84">
-        <v>-80.78145369469389</v>
+        <v>-82.03157097469389</v>
       </c>
       <c r="P84">
-        <v>-323.1258147787756</v>
+        <v>-328.1262838987756</v>
       </c>
       <c r="Q84">
-        <v>-304.7258147787755</v>
+        <v>-309.7262838987756</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3398368009853988</v>
+        <v>0.3571330833963046</v>
       </c>
       <c r="T84">
-        <v>5.577769461372994</v>
+        <v>5.905873547336112</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.04239243869925806</v>
+        <v>0.04188168642577302</v>
       </c>
       <c r="W84">
-        <v>0.225803862954715</v>
+        <v>0.2259242983408027</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2119621934962903</v>
+        <v>0.2094084321288652</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.248229791800238</v>
+        <v>0.2501297918002381</v>
       </c>
       <c r="C85">
-        <v>-1435.722755379508</v>
+        <v>-1468.584005942442</v>
       </c>
       <c r="D85">
-        <v>683.2412446204926</v>
+        <v>676.8879940575589</v>
       </c>
       <c r="E85">
-        <v>1659.264</v>
+        <v>1685.772</v>
       </c>
       <c r="F85">
-        <v>2200.164</v>
+        <v>2226.672</v>
       </c>
       <c r="G85">
         <v>81.2</v>
@@ -8257,37 +8257,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M85">
-        <v>518.7986712000001</v>
+        <v>525.0492576000001</v>
       </c>
       <c r="N85">
-        <v>-410.1578548734694</v>
+        <v>-416.4084412734695</v>
       </c>
       <c r="O85">
-        <v>-82.03157097469389</v>
+        <v>-83.2816882546939</v>
       </c>
       <c r="P85">
-        <v>-328.1262838987756</v>
+        <v>-333.1267530187756</v>
       </c>
       <c r="Q85">
-        <v>-309.7262838987756</v>
+        <v>-314.7267530187756</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3571330833963046</v>
+        <v>0.3765914011085738</v>
       </c>
       <c r="T85">
-        <v>5.905873547336112</v>
+        <v>6.274990644044621</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.04188168642577302</v>
+        <v>0.04138309492070429</v>
       </c>
       <c r="W85">
-        <v>0.2259242983408027</v>
+        <v>0.226041866217698</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2094084321288652</v>
+        <v>0.2069154746035214</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.250129791800238</v>
+        <v>0.252029791800238</v>
       </c>
       <c r="C86">
-        <v>-1468.584005942441</v>
+        <v>-1501.328191206863</v>
       </c>
       <c r="D86">
-        <v>676.8879940575592</v>
+        <v>670.6518087931377</v>
       </c>
       <c r="E86">
-        <v>1685.772</v>
+        <v>1712.28</v>
       </c>
       <c r="F86">
-        <v>2226.672</v>
+        <v>2253.18</v>
       </c>
       <c r="G86">
         <v>81.2</v>
@@ -8339,37 +8339,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M86">
-        <v>525.0492576</v>
+        <v>531.2998440000001</v>
       </c>
       <c r="N86">
-        <v>-416.4084412734694</v>
+        <v>-422.6590276734695</v>
       </c>
       <c r="O86">
-        <v>-83.28168825469389</v>
+        <v>-84.5318055346939</v>
       </c>
       <c r="P86">
-        <v>-333.1267530187755</v>
+        <v>-338.1272221387756</v>
       </c>
       <c r="Q86">
-        <v>-314.7267530187755</v>
+        <v>-319.7272221387756</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3765914011085735</v>
+        <v>0.3986441611824784</v>
       </c>
       <c r="T86">
-        <v>6.274990644044616</v>
+        <v>6.693323353647592</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.0413830949207043</v>
+        <v>0.04089623498046072</v>
       </c>
       <c r="W86">
-        <v>0.2260418662176979</v>
+        <v>0.2261566677916074</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2069154746035216</v>
+        <v>0.2044811749023036</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.252029791800238</v>
+        <v>0.2539297918002381</v>
       </c>
       <c r="C87">
-        <v>-1501.328191206863</v>
+        <v>-1533.958517211637</v>
       </c>
       <c r="D87">
-        <v>670.6518087931377</v>
+        <v>664.5294827883628</v>
       </c>
       <c r="E87">
-        <v>1712.28</v>
+        <v>1738.788</v>
       </c>
       <c r="F87">
-        <v>2253.18</v>
+        <v>2279.688</v>
       </c>
       <c r="G87">
         <v>81.2</v>
@@ -8421,37 +8421,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M87">
-        <v>531.2998440000001</v>
+        <v>537.5504304000001</v>
       </c>
       <c r="N87">
-        <v>-422.6590276734695</v>
+        <v>-428.9096140734695</v>
       </c>
       <c r="O87">
-        <v>-84.5318055346939</v>
+        <v>-85.7819228146939</v>
       </c>
       <c r="P87">
-        <v>-338.1272221387756</v>
+        <v>-343.1276912587756</v>
       </c>
       <c r="Q87">
-        <v>-319.7272221387756</v>
+        <v>-324.7276912587756</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3986441611824784</v>
+        <v>0.4238473155526555</v>
       </c>
       <c r="T87">
-        <v>6.693323353647592</v>
+        <v>7.171417878908134</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.04089623498046072</v>
+        <v>0.04042069736440884</v>
       </c>
       <c r="W87">
-        <v>0.2261566677916074</v>
+        <v>0.2262687995614724</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2044811749023036</v>
+        <v>0.2021034868220443</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2539297918002381</v>
+        <v>0.2558297918002381</v>
       </c>
       <c r="C88">
-        <v>-1533.958517211637</v>
+        <v>-1566.478073984016</v>
       </c>
       <c r="D88">
-        <v>664.5294827883628</v>
+        <v>658.5179260159846</v>
       </c>
       <c r="E88">
-        <v>1738.788</v>
+        <v>1765.296</v>
       </c>
       <c r="F88">
-        <v>2279.688</v>
+        <v>2306.196</v>
       </c>
       <c r="G88">
         <v>81.2</v>
@@ -8503,37 +8503,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M88">
-        <v>537.5504304000001</v>
+        <v>543.8010168000001</v>
       </c>
       <c r="N88">
-        <v>-428.9096140734695</v>
+        <v>-435.1602004734694</v>
       </c>
       <c r="O88">
-        <v>-85.7819228146939</v>
+        <v>-87.0320400946939</v>
       </c>
       <c r="P88">
-        <v>-343.1276912587756</v>
+        <v>-348.1281603787755</v>
       </c>
       <c r="Q88">
-        <v>-324.7276912587756</v>
+        <v>-329.7281603787756</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4238473155526555</v>
+        <v>0.4529278782874751</v>
       </c>
       <c r="T88">
-        <v>7.171417878908134</v>
+        <v>7.723065408054913</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.04042069736440884</v>
+        <v>0.03995609164757656</v>
       </c>
       <c r="W88">
-        <v>0.2262687995614724</v>
+        <v>0.2263783535895015</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2021034868220443</v>
+        <v>0.1997804582378828</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2558297918002381</v>
+        <v>0.257729791800238</v>
       </c>
       <c r="C89">
-        <v>-1566.478073984016</v>
+        <v>-1598.889840739987</v>
       </c>
       <c r="D89">
-        <v>658.5179260159846</v>
+        <v>652.6141592600126</v>
       </c>
       <c r="E89">
-        <v>1765.296</v>
+        <v>1791.804</v>
       </c>
       <c r="F89">
-        <v>2306.196</v>
+        <v>2332.704</v>
       </c>
       <c r="G89">
         <v>81.2</v>
@@ -8585,37 +8585,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M89">
-        <v>543.8010168000001</v>
+        <v>550.0516032</v>
       </c>
       <c r="N89">
-        <v>-435.1602004734694</v>
+        <v>-441.4107868734694</v>
       </c>
       <c r="O89">
-        <v>-87.0320400946939</v>
+        <v>-88.2821573746939</v>
       </c>
       <c r="P89">
-        <v>-348.1281603787755</v>
+        <v>-353.1286294987755</v>
       </c>
       <c r="Q89">
-        <v>-329.7281603787756</v>
+        <v>-334.7286294987755</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4529278782874751</v>
+        <v>0.4868552014780981</v>
       </c>
       <c r="T89">
-        <v>7.723065408054913</v>
+        <v>8.366654192059491</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03995609164757656</v>
+        <v>0.03950204515158137</v>
       </c>
       <c r="W89">
-        <v>0.2263783535895015</v>
+        <v>0.2264854177532571</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1997804582378828</v>
+        <v>0.1975102257579069</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.257729791800238</v>
+        <v>0.259629791800238</v>
       </c>
       <c r="C90">
-        <v>-1598.889840739987</v>
+        <v>-1631.196690807393</v>
       </c>
       <c r="D90">
-        <v>652.6141592600126</v>
+        <v>646.8153091926073</v>
       </c>
       <c r="E90">
-        <v>1791.804</v>
+        <v>1818.312</v>
       </c>
       <c r="F90">
-        <v>2332.704</v>
+        <v>2359.212</v>
       </c>
       <c r="G90">
         <v>81.2</v>
@@ -8667,37 +8667,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M90">
-        <v>550.0516032</v>
+        <v>556.3021896</v>
       </c>
       <c r="N90">
-        <v>-441.4107868734694</v>
+        <v>-447.6613732734694</v>
       </c>
       <c r="O90">
-        <v>-88.2821573746939</v>
+        <v>-89.53227465469388</v>
       </c>
       <c r="P90">
-        <v>-353.1286294987755</v>
+        <v>-358.1290986187755</v>
       </c>
       <c r="Q90">
-        <v>-334.7286294987755</v>
+        <v>-339.7290986187755</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4868552014780981</v>
+        <v>0.5269511288851978</v>
       </c>
       <c r="T90">
-        <v>8.366654192059491</v>
+        <v>9.127259118610352</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03950204515158137</v>
+        <v>0.03905820194763102</v>
       </c>
       <c r="W90">
-        <v>0.2264854177532571</v>
+        <v>0.2265900759807486</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1975102257579069</v>
+        <v>0.1952910097381552</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.259629791800238</v>
+        <v>0.261529791800238</v>
       </c>
       <c r="C91">
-        <v>-1631.196690807393</v>
+        <v>-1663.401396288868</v>
       </c>
       <c r="D91">
-        <v>646.8153091926073</v>
+        <v>641.1186037111322</v>
       </c>
       <c r="E91">
-        <v>1818.312</v>
+        <v>1844.82</v>
       </c>
       <c r="F91">
-        <v>2359.212</v>
+        <v>2385.72</v>
       </c>
       <c r="G91">
         <v>81.2</v>
@@ -8749,37 +8749,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M91">
-        <v>556.3021896</v>
+        <v>562.5527760000001</v>
       </c>
       <c r="N91">
-        <v>-447.6613732734694</v>
+        <v>-453.9119596734695</v>
       </c>
       <c r="O91">
-        <v>-89.53227465469388</v>
+        <v>-90.78239193469391</v>
       </c>
       <c r="P91">
-        <v>-358.1290986187755</v>
+        <v>-363.1295677387756</v>
       </c>
       <c r="Q91">
-        <v>-339.7290986187755</v>
+        <v>-344.7295677387756</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5269511288851978</v>
+        <v>0.5750662417737177</v>
       </c>
       <c r="T91">
-        <v>9.127259118610352</v>
+        <v>10.03998503047139</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03905820194763102</v>
+        <v>0.03862422192599067</v>
       </c>
       <c r="W91">
-        <v>0.2265900759807486</v>
+        <v>0.2266924084698514</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1952910097381552</v>
+        <v>0.1931211096299533</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.261529791800238</v>
+        <v>0.263429791800238</v>
       </c>
       <c r="C92">
-        <v>-1663.401396288868</v>
+        <v>-1695.506632480544</v>
       </c>
       <c r="D92">
-        <v>641.1186037111322</v>
+        <v>635.5213675194562</v>
       </c>
       <c r="E92">
-        <v>1844.82</v>
+        <v>1871.328</v>
       </c>
       <c r="F92">
-        <v>2385.72</v>
+        <v>2412.228</v>
       </c>
       <c r="G92">
         <v>81.2</v>
@@ -8831,37 +8831,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M92">
-        <v>562.5527760000001</v>
+        <v>568.8033624000001</v>
       </c>
       <c r="N92">
-        <v>-453.9119596734695</v>
+        <v>-460.1625460734695</v>
       </c>
       <c r="O92">
-        <v>-90.78239193469391</v>
+        <v>-92.0325092146939</v>
       </c>
       <c r="P92">
-        <v>-363.1295677387756</v>
+        <v>-368.1300368587756</v>
       </c>
       <c r="Q92">
-        <v>-344.7295677387756</v>
+        <v>-349.7300368587755</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5750662417737177</v>
+        <v>0.6338736019707975</v>
       </c>
       <c r="T92">
-        <v>10.03998503047139</v>
+        <v>11.15553892274599</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03862422192599067</v>
+        <v>0.03819977992680396</v>
       </c>
       <c r="W92">
-        <v>0.2266924084698514</v>
+        <v>0.2267924918932596</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1931211096299533</v>
+        <v>0.1909988996340198</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.263429791800238</v>
+        <v>0.265329791800238</v>
       </c>
       <c r="C93">
-        <v>-1695.506632480544</v>
+        <v>-1727.514982061278</v>
       </c>
       <c r="D93">
-        <v>635.5213675194562</v>
+        <v>630.0210179387227</v>
       </c>
       <c r="E93">
-        <v>1871.328</v>
+        <v>1897.836</v>
       </c>
       <c r="F93">
-        <v>2412.228</v>
+        <v>2438.736</v>
       </c>
       <c r="G93">
         <v>81.2</v>
@@ -8913,37 +8913,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M93">
-        <v>568.8033624000001</v>
+        <v>575.0539488000001</v>
       </c>
       <c r="N93">
-        <v>-460.1625460734695</v>
+        <v>-466.4131324734694</v>
       </c>
       <c r="O93">
-        <v>-92.0325092146939</v>
+        <v>-93.28262649469389</v>
       </c>
       <c r="P93">
-        <v>-368.1300368587756</v>
+        <v>-373.1305059787755</v>
       </c>
       <c r="Q93">
-        <v>-349.7300368587755</v>
+        <v>-354.7305059787756</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6338736019707975</v>
+        <v>0.7073828022171473</v>
       </c>
       <c r="T93">
-        <v>11.15553892274599</v>
+        <v>12.54998128808924</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03819977992680396</v>
+        <v>0.03778456492759957</v>
       </c>
       <c r="W93">
-        <v>0.2267924918932596</v>
+        <v>0.226890399590072</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1909988996340198</v>
+        <v>0.1889228246379979</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.265329791800238</v>
+        <v>0.267229791800238</v>
       </c>
       <c r="C94">
-        <v>-1727.514982061278</v>
+        <v>-1759.428939066212</v>
       </c>
       <c r="D94">
-        <v>630.0210179387227</v>
+        <v>624.6150609337886</v>
       </c>
       <c r="E94">
-        <v>1897.836</v>
+        <v>1924.344</v>
       </c>
       <c r="F94">
-        <v>2438.736</v>
+        <v>2465.244</v>
       </c>
       <c r="G94">
         <v>81.2</v>
@@ -8995,37 +8995,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M94">
-        <v>575.0539488000001</v>
+        <v>581.3045352</v>
       </c>
       <c r="N94">
-        <v>-466.4131324734694</v>
+        <v>-472.6637188734694</v>
       </c>
       <c r="O94">
-        <v>-93.28262649469389</v>
+        <v>-94.53274377469388</v>
       </c>
       <c r="P94">
-        <v>-373.1305059787755</v>
+        <v>-378.1309750987755</v>
       </c>
       <c r="Q94">
-        <v>-354.7305059787756</v>
+        <v>-359.7309750987755</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7073828022171473</v>
+        <v>0.8018946311053113</v>
       </c>
       <c r="T94">
-        <v>12.54998128808924</v>
+        <v>14.34283575781628</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03778456492759957</v>
+        <v>0.03737827928321678</v>
       </c>
       <c r="W94">
-        <v>0.226890399590072</v>
+        <v>0.2269862017450175</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1889228246379979</v>
+        <v>0.186891396416084</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.267229791800238</v>
+        <v>0.269129791800238</v>
       </c>
       <c r="C95">
-        <v>-1759.428939066212</v>
+        <v>-1791.250912657499</v>
       </c>
       <c r="D95">
-        <v>624.6150609337886</v>
+        <v>619.3010873425011</v>
       </c>
       <c r="E95">
-        <v>1924.344</v>
+        <v>1950.852</v>
       </c>
       <c r="F95">
-        <v>2465.244</v>
+        <v>2491.752</v>
       </c>
       <c r="G95">
         <v>81.2</v>
@@ -9077,37 +9077,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M95">
-        <v>581.3045352</v>
+        <v>587.5551216000001</v>
       </c>
       <c r="N95">
-        <v>-472.6637188734694</v>
+        <v>-478.9143052734695</v>
       </c>
       <c r="O95">
-        <v>-94.53274377469388</v>
+        <v>-95.78286105469391</v>
       </c>
       <c r="P95">
-        <v>-378.1309750987755</v>
+        <v>-383.1314442187756</v>
       </c>
       <c r="Q95">
-        <v>-359.7309750987755</v>
+        <v>-364.7314442187756</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8018946311053113</v>
+        <v>0.9279104029561969</v>
       </c>
       <c r="T95">
-        <v>14.34283575781628</v>
+        <v>16.733308384119</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03737827928321678</v>
+        <v>0.03698063801424639</v>
       </c>
       <c r="W95">
-        <v>0.2269862017450175</v>
+        <v>0.2270799655562407</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.186891396416084</v>
+        <v>0.1849031900712319</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.269129791800238</v>
+        <v>0.2710297918002381</v>
       </c>
       <c r="C96">
-        <v>-1791.250912657499</v>
+        <v>-1822.983230704174</v>
       </c>
       <c r="D96">
-        <v>619.3010873425011</v>
+        <v>614.0767692958266</v>
       </c>
       <c r="E96">
-        <v>1950.852</v>
+        <v>1977.36</v>
       </c>
       <c r="F96">
-        <v>2491.752</v>
+        <v>2518.26</v>
       </c>
       <c r="G96">
         <v>81.2</v>
@@ -9159,37 +9159,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M96">
-        <v>587.5551216000001</v>
+        <v>593.8057080000001</v>
       </c>
       <c r="N96">
-        <v>-478.9143052734695</v>
+        <v>-485.1648916734695</v>
       </c>
       <c r="O96">
-        <v>-95.78286105469391</v>
+        <v>-97.03297833469389</v>
       </c>
       <c r="P96">
-        <v>-383.1314442187756</v>
+        <v>-388.1319133387756</v>
       </c>
       <c r="Q96">
-        <v>-364.7314442187756</v>
+        <v>-369.7319133387756</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9279104029561969</v>
+        <v>1.104332483547437</v>
       </c>
       <c r="T96">
-        <v>16.733308384119</v>
+        <v>20.0799700609428</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03698063801424639</v>
+        <v>0.03659136814041222</v>
       </c>
       <c r="W96">
-        <v>0.2270799655562407</v>
+        <v>0.2271717553924908</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1849031900712319</v>
+        <v>0.1829568407020611</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2710297918002381</v>
+        <v>0.272929791800238</v>
       </c>
       <c r="C97">
-        <v>-1822.983230704174</v>
+        <v>-1854.628143182341</v>
       </c>
       <c r="D97">
-        <v>614.0767692958266</v>
+        <v>608.9398568176598</v>
       </c>
       <c r="E97">
-        <v>1977.36</v>
+        <v>2003.868</v>
       </c>
       <c r="F97">
-        <v>2518.26</v>
+        <v>2544.768</v>
       </c>
       <c r="G97">
         <v>81.2</v>
@@ -9241,37 +9241,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M97">
-        <v>593.8057080000001</v>
+        <v>600.0562944000002</v>
       </c>
       <c r="N97">
-        <v>-485.1648916734695</v>
+        <v>-491.4154780734696</v>
       </c>
       <c r="O97">
-        <v>-97.03297833469389</v>
+        <v>-98.28309561469392</v>
       </c>
       <c r="P97">
-        <v>-388.1319133387756</v>
+        <v>-393.1323824587756</v>
       </c>
       <c r="Q97">
-        <v>-369.7319133387756</v>
+        <v>-374.7323824587756</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.104332483547437</v>
+        <v>1.368965604434297</v>
       </c>
       <c r="T97">
-        <v>20.0799700609428</v>
+        <v>25.09996257617851</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03659136814041222</v>
+        <v>0.03621020805561625</v>
       </c>
       <c r="W97">
-        <v>0.2271717553924908</v>
+        <v>0.2272616329404857</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1829568407020611</v>
+        <v>0.1810510402780813</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2729297918002381</v>
+        <v>0.274829791800238</v>
       </c>
       <c r="C98">
-        <v>-1854.62814318234</v>
+        <v>-1886.187825406122</v>
       </c>
       <c r="D98">
-        <v>608.9398568176598</v>
+        <v>603.8881745938787</v>
       </c>
       <c r="E98">
-        <v>2003.868</v>
+        <v>2030.376</v>
       </c>
       <c r="F98">
-        <v>2544.768</v>
+        <v>2571.276</v>
       </c>
       <c r="G98">
         <v>81.2</v>
@@ -9323,37 +9323,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M98">
-        <v>600.0562944000001</v>
+        <v>606.3068808</v>
       </c>
       <c r="N98">
-        <v>-491.4154780734694</v>
+        <v>-497.6660644734694</v>
       </c>
       <c r="O98">
-        <v>-98.28309561469389</v>
+        <v>-99.53321289469389</v>
       </c>
       <c r="P98">
-        <v>-393.1323824587756</v>
+        <v>-398.1328515787756</v>
       </c>
       <c r="Q98">
-        <v>-374.7323824587755</v>
+        <v>-379.7328515787756</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.368965604434293</v>
+        <v>1.810020805912391</v>
       </c>
       <c r="T98">
-        <v>25.09996257617845</v>
+        <v>33.46661676823793</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03621020805561626</v>
+        <v>0.03583690694164084</v>
       </c>
       <c r="W98">
-        <v>0.2272616329404857</v>
+        <v>0.2273496573431611</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1810510402780813</v>
+        <v>0.1791845347082042</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.274829791800238</v>
+        <v>0.276729791800238</v>
       </c>
       <c r="C99">
-        <v>-1886.187825406122</v>
+        <v>-1917.664381099104</v>
       </c>
       <c r="D99">
-        <v>603.8881745938787</v>
+        <v>598.919618900896</v>
       </c>
       <c r="E99">
-        <v>2030.376</v>
+        <v>2056.884</v>
       </c>
       <c r="F99">
-        <v>2571.276</v>
+        <v>2597.784</v>
       </c>
       <c r="G99">
         <v>81.2</v>
@@ -9405,37 +9405,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M99">
-        <v>606.3068808</v>
+        <v>612.5574672</v>
       </c>
       <c r="N99">
-        <v>-497.6660644734694</v>
+        <v>-503.9166508734694</v>
       </c>
       <c r="O99">
-        <v>-99.53321289469389</v>
+        <v>-100.7833301746939</v>
       </c>
       <c r="P99">
-        <v>-398.1328515787756</v>
+        <v>-403.1333206987755</v>
       </c>
       <c r="Q99">
-        <v>-379.7328515787756</v>
+        <v>-384.7333206987755</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.810020805912391</v>
+        <v>2.692131208868586</v>
       </c>
       <c r="T99">
-        <v>33.46661676823793</v>
+        <v>50.19992515235689</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03583690694164084</v>
+        <v>0.03547122421774654</v>
       </c>
       <c r="W99">
-        <v>0.2273496573431611</v>
+        <v>0.2274358853294554</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1791845347082042</v>
+        <v>0.1773561210887328</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.276729791800238</v>
+        <v>0.2786297918002381</v>
       </c>
       <c r="C100">
-        <v>-1917.664381099104</v>
+        <v>-1949.059845315402</v>
       </c>
       <c r="D100">
-        <v>598.919618900896</v>
+        <v>594.0321546845984</v>
       </c>
       <c r="E100">
-        <v>2056.884</v>
+        <v>2083.392</v>
       </c>
       <c r="F100">
-        <v>2597.784</v>
+        <v>2624.292</v>
       </c>
       <c r="G100">
         <v>81.2</v>
@@ -9487,37 +9487,37 @@
         <v>108.6408163265306</v>
       </c>
       <c r="M100">
-        <v>612.5574672</v>
+        <v>618.8080536000001</v>
       </c>
       <c r="N100">
-        <v>-503.9166508734694</v>
+        <v>-510.1672372734695</v>
       </c>
       <c r="O100">
-        <v>-100.7833301746939</v>
+        <v>-102.0334474546939</v>
       </c>
       <c r="P100">
-        <v>-403.1333206987755</v>
+        <v>-408.1337898187756</v>
       </c>
       <c r="Q100">
-        <v>-384.7333206987755</v>
+        <v>-389.7337898187756</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.692131208868586</v>
+        <v>5.338462417737172</v>
       </c>
       <c r="T100">
-        <v>50.19992515235689</v>
+        <v>100.3998503047138</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03547122421774654</v>
+        <v>0.03511292902362789</v>
       </c>
       <c r="W100">
-        <v>0.2274358853294554</v>
+        <v>0.2275203713362286</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1773561210887328</v>
+        <v>0.1755646451181394</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2786297918002381</v>
-      </c>
-      <c r="C101">
-        <v>-1949.059845315402</v>
-      </c>
-      <c r="D101">
-        <v>594.0321546845984</v>
-      </c>
-      <c r="E101">
-        <v>2083.392</v>
-      </c>
-      <c r="F101">
-        <v>2624.292</v>
-      </c>
-      <c r="G101">
-        <v>81.2</v>
-      </c>
-      <c r="H101">
-        <v>2109.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>127.0408163265306</v>
-      </c>
-      <c r="K101">
-        <v>18.40000000000001</v>
-      </c>
-      <c r="L101">
-        <v>108.6408163265306</v>
-      </c>
-      <c r="M101">
-        <v>618.8080536000001</v>
-      </c>
-      <c r="N101">
-        <v>-510.1672372734695</v>
-      </c>
-      <c r="O101">
-        <v>-102.0334474546939</v>
-      </c>
-      <c r="P101">
-        <v>-408.1337898187756</v>
-      </c>
-      <c r="Q101">
-        <v>-389.7337898187756</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.338462417737172</v>
-      </c>
-      <c r="T101">
-        <v>100.3998503047138</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03511292902362789</v>
-      </c>
-      <c r="W101">
-        <v>0.2275203713362286</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1755646451181394</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
